--- a/DocDesign/RandomTool/Game.55/excel/Language.xlsx
+++ b/DocDesign/RandomTool/Game.55/excel/Language.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="430"/>
+    <workbookView windowWidth="21600" windowHeight="11865"/>
   </bookViews>
   <sheets>
     <sheet name="Language" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="560">
   <si>
     <t>编号【KEY】</t>
   </si>
@@ -125,6 +125,468 @@
     <t>client_no</t>
   </si>
   <si>
+    <t>common_confirm</t>
+  </si>
+  <si>
+    <t>确认</t>
+  </si>
+  <si>
+    <t>Confirm</t>
+  </si>
+  <si>
+    <t>تأكيد</t>
+  </si>
+  <si>
+    <t>Xác nhận</t>
+  </si>
+  <si>
+    <t>নিশ্চিত করুন</t>
+  </si>
+  <si>
+    <t>Confirmar</t>
+  </si>
+  <si>
+    <t>कन्फ़र्म करें</t>
+  </si>
+  <si>
+    <t>Konfirmasi</t>
+  </si>
+  <si>
+    <t>ยืนยัน</t>
+  </si>
+  <si>
+    <t>Onayla</t>
+  </si>
+  <si>
+    <t>تصدیق کریں۔</t>
+  </si>
+  <si>
+    <t>Kumpirmahin</t>
+  </si>
+  <si>
+    <t>common_cancel</t>
+  </si>
+  <si>
+    <t>取消</t>
+  </si>
+  <si>
+    <t>Cancel</t>
+  </si>
+  <si>
+    <t>إلغاء</t>
+  </si>
+  <si>
+    <t>Hủy</t>
+  </si>
+  <si>
+    <t>বাতিল করুন</t>
+  </si>
+  <si>
+    <t>Cancelar</t>
+  </si>
+  <si>
+    <t>कैंसल करें</t>
+  </si>
+  <si>
+    <t>Batal</t>
+  </si>
+  <si>
+    <t>ยกเลิก</t>
+  </si>
+  <si>
+    <t>İptal</t>
+  </si>
+  <si>
+    <t>منسوخ کریں۔</t>
+  </si>
+  <si>
+    <t>Kanselahin</t>
+  </si>
+  <si>
+    <t>common_exit</t>
+  </si>
+  <si>
+    <t>退出</t>
+  </si>
+  <si>
+    <t>Exit</t>
+  </si>
+  <si>
+    <t>مخرج</t>
+  </si>
+  <si>
+    <t>Thoát</t>
+  </si>
+  <si>
+    <t>প্রস্থান করুন</t>
+  </si>
+  <si>
+    <t>Salir</t>
+  </si>
+  <si>
+    <t>बाहर निकलें</t>
+  </si>
+  <si>
+    <t>Keluar</t>
+  </si>
+  <si>
+    <t>Sair</t>
+  </si>
+  <si>
+    <t>ออก</t>
+  </si>
+  <si>
+    <t>Çıkış</t>
+  </si>
+  <si>
+    <t>باہر نکلیں۔</t>
+  </si>
+  <si>
+    <t>Lumabas</t>
+  </si>
+  <si>
+    <t>common_hint</t>
+  </si>
+  <si>
+    <t>提示</t>
+  </si>
+  <si>
+    <t>Warning</t>
+  </si>
+  <si>
+    <t>تحذير</t>
+  </si>
+  <si>
+    <t>Cảnh báo</t>
+  </si>
+  <si>
+    <t>সতর্কবার্তা</t>
+  </si>
+  <si>
+    <t>Advertencia</t>
+  </si>
+  <si>
+    <t>चेतावनी</t>
+  </si>
+  <si>
+    <t>Peringatan</t>
+  </si>
+  <si>
+    <t>Aviso</t>
+  </si>
+  <si>
+    <t>คำเตือน</t>
+  </si>
+  <si>
+    <t>Uyarı</t>
+  </si>
+  <si>
+    <t>وارننگ</t>
+  </si>
+  <si>
+    <t>Babala</t>
+  </si>
+  <si>
+    <t>common_reconnect</t>
+  </si>
+  <si>
+    <t>重新连接</t>
+  </si>
+  <si>
+    <t>reconnect</t>
+  </si>
+  <si>
+    <t>إعادة الاتصال</t>
+  </si>
+  <si>
+    <t>Kết nối lại</t>
+  </si>
+  <si>
+    <t>পুনরায় সংযোগ করুন</t>
+  </si>
+  <si>
+    <t>reconectar</t>
+  </si>
+  <si>
+    <t>फिर से कनेक्ट करें</t>
+  </si>
+  <si>
+    <t>sambungkan kembali</t>
+  </si>
+  <si>
+    <t>Reconectar</t>
+  </si>
+  <si>
+    <t>เชื่อมต่อใหม่</t>
+  </si>
+  <si>
+    <t>yeniden bağlan</t>
+  </si>
+  <si>
+    <t>دوبارہ جڑیں</t>
+  </si>
+  <si>
+    <t>muling kumonekta</t>
+  </si>
+  <si>
+    <t>common_tip_disconnected</t>
+  </si>
+  <si>
+    <t>您已经断开连接！
+请尝试重连</t>
+  </si>
+  <si>
+    <t>You've disconnected!
+Please try reconnecting.</t>
+  </si>
+  <si>
+    <t>!لقد انقطع الاتصال
+يرجى محاولة إعادة الاتصال</t>
+  </si>
+  <si>
+    <t>Bạn đã bị ngắt kết nối!
+Vui lòng thử kết nối lại.</t>
+  </si>
+  <si>
+    <t>আপনার সংযোগ বিচ্ছিন্ন হয়ে গেছে!
+অনুগ্রহ করে পুনরায় সংযোগ করার চেষ্টা করুন।</t>
+  </si>
+  <si>
+    <t>¡Te has desconectado!
+Intenta volver a conectarte.</t>
+  </si>
+  <si>
+    <t>आप डिस्कनेक्ट हो गए हैं!
+कृपया फिर से कनेक्ट करने का प्रयास करें।</t>
+  </si>
+  <si>
+    <t>Anda telah terputus!
+Silakan coba sambungkan kembali.</t>
+  </si>
+  <si>
+    <t>Você foi desligado!
+Por favor, tente reconectar-se.</t>
+  </si>
+  <si>
+    <t>คุณหลุดการเชื่อมต่อ!
+โปรดลองเชื่อมต่อใหม่</t>
+  </si>
+  <si>
+    <t>Bağlantınız kesildi!
+Lütfen yeniden bağlanmayı deneyin.</t>
+  </si>
+  <si>
+    <t>آپ کا رابطہ منقطع ہو گیا ہے!
+براہ کرم دوبارہ منسلک کرنے کی کوشش کریں۔</t>
+  </si>
+  <si>
+    <t>Nadiskonekta ka na!
+Pakisubukang kumonekta muli.</t>
+  </si>
+  <si>
+    <t>common_tip_kickout</t>
+  </si>
+  <si>
+    <t>警告：
+请勿重复登录!</t>
+  </si>
+  <si>
+    <t>Warning: 
+Please do not log in repeatedly!</t>
+  </si>
+  <si>
+    <t>:تحذير
+ !يرجى عدم تسجيل الدخول بشكل متكرر.</t>
+  </si>
+  <si>
+    <t>Cảnh báo:
+Vui lòng không đăng nhập nhiều lần!</t>
+  </si>
+  <si>
+    <t>সতর্কীকরণ:
+অনুগ্রহ করে বারবার লগ ইন করবেন না!</t>
+  </si>
+  <si>
+    <t>Advertencia:
+¡No inicie sesión repetidamente!</t>
+  </si>
+  <si>
+    <t>चेतावनी:
+कृपया बार-बार लॉग इन न करें!</t>
+  </si>
+  <si>
+    <t>Peringatan:
+Mohon jangan masuk berulang kali!</t>
+  </si>
+  <si>
+    <t>Aviso:
+Por favor, não inicie sessão repetidamente!</t>
+  </si>
+  <si>
+    <t>คำเตือน:
+โปรดอย่าล็อกอินซ้ำๆ!</t>
+  </si>
+  <si>
+    <t>Uyarı:
+Lütfen tekrar tekrar giriş yapmayın!</t>
+  </si>
+  <si>
+    <t>انتباہ:
+براہ کرم بار بار لاگ ان نہ کریں!</t>
+  </si>
+  <si>
+    <t>Babala:
+Huwag mag-log in nang paulit-ulit!</t>
+  </si>
+  <si>
+    <t>common_recharge</t>
+  </si>
+  <si>
+    <t>余额不足！
+需要充值吗?</t>
+  </si>
+  <si>
+    <t>Insufficient balance!
+Would you like to recharge?</t>
+  </si>
+  <si>
+    <t>رصيدك غير كافٍ!
+هل ترغب في إعادة شحن رصيدك؟</t>
+  </si>
+  <si>
+    <t>Số dư không đủ!
+Bạn có muốn nạp tiền không?</t>
+  </si>
+  <si>
+    <t>ব্যালেন্স অপর্যাপ্ত!
+আপনি কি রিচার্জ করতে চান?</t>
+  </si>
+  <si>
+    <t>¡Saldo insuficiente!
+¿Quieres recargar?</t>
+  </si>
+  <si>
+    <t>बैलेंस कम है!
+क्या आप रिचार्ज करना चाहेंगे?</t>
+  </si>
+  <si>
+    <t>Saldo tidak mencukupi!
+Apakah Anda ingin mengisi ulang saldo?</t>
+  </si>
+  <si>
+    <t>Saldo insuficiente!
+Deseja recarregar?</t>
+  </si>
+  <si>
+    <t>ยอดเงินไม่เพียงพอ!
+คุณต้องการเติมเงินหรือไม่?</t>
+  </si>
+  <si>
+    <t>Bakiyeniz yetersiz!
+Yükleme yapmak ister misiniz?</t>
+  </si>
+  <si>
+    <t>ناکافی توازن!
+کیا آپ ری چارج کرنا چاہیں گے؟</t>
+  </si>
+  <si>
+    <t>Kulang ang balanse!
+Gusto mo bang mag-recharge?</t>
+  </si>
+  <si>
+    <t>common_tip_maintain</t>
+  </si>
+  <si>
+    <t>游戏服务器维护中，暂时无法游玩，请稍后再尝试。</t>
+  </si>
+  <si>
+    <t>The game server is under maintenance and cannot be played temporarily. 
+Please try again later.</t>
+  </si>
+  <si>
+    <t>خادم اللعبة يخضع للصيانة ولا يمكن اللعب عليه مؤقتًا. يرجى المحاولة مرة أخرى لاحقًا.</t>
+  </si>
+  <si>
+    <t>Máy chủ trò chơi đang được bảo trì và tạm thời không thể chơi được.
+Vui lòng thử lại sau.</t>
+  </si>
+  <si>
+    <t>গেম সার্ভারটি রক্ষণাবেক্ষণের অধীনে থাকায় আপাতত খেলা যাচ্ছে না।
+অনুগ্রহ করে পরে আবার চেষ্টা করুন।</t>
+  </si>
+  <si>
+    <t>El servidor del juego está en mantenimiento y no se puede jugar temporalmente.
+Por favor, inténtalo de nuevo más tarde.</t>
+  </si>
+  <si>
+    <t>गेम सर्वर मेंटेनेंस में है और इसे कुछ समय के लिए नहीं खेला जा सकता। कृपया बाद में फिर से कोशिश करें।</t>
+  </si>
+  <si>
+    <t>Server game sedang dalam perbaikan dan tidak dapat dimainkan untuk sementara waktu.
+Silakan coba lagi nanti.</t>
+  </si>
+  <si>
+    <t>O servidor de jogo está em manutenção e não está disponível temporariamente.
+Por favor, tente mais tarde.</t>
+  </si>
+  <si>
+    <t>เซิร์ฟเวอร์เกมกำลังอยู่ในระหว่างการปรับปรุงและไม่สามารถเล่นได้ชั่วคราว
+โปรดลองใหม่อีกครั้งในภายหลัง</t>
+  </si>
+  <si>
+    <t>Oyun sunucusu bakımda olduğundan geçici olarak oynanamaz.
+Lütfen daha sonra tekrar deneyin.</t>
+  </si>
+  <si>
+    <t>گیم سرور کی دیکھ بھال جاری ہے اور اسے عارضی طور پر نہیں چلایا جا سکتا۔
+براہ کرم بعد میں دوبارہ کوشش کریں۔</t>
+  </si>
+  <si>
+    <t>Ang server ng laro ay nasa ilalim ng maintenance at hindi maaaring laruin pansamantala. Pakisubukang muli mamaya.</t>
+  </si>
+  <si>
+    <t>common_tip_long_time_noplay</t>
+  </si>
+  <si>
+    <t>哎呀！您很久没玩游戏了~ 请重新进入游戏，展现您的实力吧！</t>
+  </si>
+  <si>
+    <t>Oops! You haven't played for a long time~ Please re-enter the game and show off your skills!</t>
+  </si>
+  <si>
+    <t>عفواً! لم تلعب منذ فترة طويلة~ يرجى العودة إلى اللعبة وإظهار مهاراتك!</t>
+  </si>
+  <si>
+    <t>Ối! Bạn đã không chơi game trong một thời gian dài rồi~ Hãy vào lại game và thể hiện kỹ năng của bạn!</t>
+  </si>
+  <si>
+    <t>ওহ! আপনি অনেকদিন ধরে খেলেননি~ অনুগ্রহ করে আবার গেমে প্রবেশ করুন এবং আপনার দক্ষতা দেখান!</t>
+  </si>
+  <si>
+    <t>¡Ups! ¡Hace mucho que no juegas! ¡Vuelve a entrar al juego y demuestra tus habilidades!</t>
+  </si>
+  <si>
+    <t>उफ़! आपने बहुत समय से नहीं खेला है~ कृपया गेम में फिर से एंटर करें और अपनी स्किल्स दिखाएं!</t>
+  </si>
+  <si>
+    <t>Ups! Kamu sudah lama tidak bermain~ Silakan masuk kembali ke permainan dan tunjukkan keahlianmu!</t>
+  </si>
+  <si>
+    <t>Ops! Há muito tempo que não joga! Por favor, volte ao jogo e mostre as suas habilidades!</t>
+  </si>
+  <si>
+    <t>โอ๊ะ! คุณไม่ได้เล่นมานานแล้ว~ กรุณาเข้าเกมอีกครั้งและโชว์ฝีมือของคุณ!</t>
+  </si>
+  <si>
+    <t>Ups! Uzun zamandır oynamadınız~ Lütfen oyuna tekrar girin ve yeteneklerinizi sergileyin!</t>
+  </si>
+  <si>
+    <t>افوہ! آپ نے طویل عرصے سے نہیں کھیلا ہے ~ براہ کرم گیم میں دوبارہ داخل ہوں اور اپنی صلاحیتوں کا مظاہرہ کریں!</t>
+  </si>
+  <si>
+    <t>Naku! Ang tagal mo nang hindi naglalaro~ Pakibalik sa laro at ipakita ang iyong mga kasanayan!</t>
+  </si>
+  <si>
     <t>common_wait</t>
   </si>
   <si>
@@ -254,6 +716,48 @@
     <t>Naabot na ang limitasyon sa pagtaya para sa round na ito.</t>
   </si>
   <si>
+    <t>common_block_5001</t>
+  </si>
+  <si>
+    <t>账号异常，目前无法参与游戏，请联系客服团队。</t>
+  </si>
+  <si>
+    <t>Account anomaly, unable to participate in the game currently, please contact the CS team</t>
+  </si>
+  <si>
+    <t>الحساب غير طبيعي، لا يمكن الانضمام إلى اللعبة حاليا، يرجى الاتصال بخدمة العملاء`</t>
+  </si>
+  <si>
+    <t>Tài khoản gặp sự cố, hiện không thể tham gia trò chơi, vui lòng liên hệ với đội ngũ hỗ trợ khách hàng.</t>
+  </si>
+  <si>
+    <t>অ্যাকাউন্টে অসঙ্গতির কারণে বর্তমানে গেমে অংশগ্রহণ করা যাচ্ছে না, অনুগ্রহ করে কাস্টমার সার্ভিস টিমের সাথে যোগাযোগ করুন।</t>
+  </si>
+  <si>
+    <t>Anomalía en la cuenta, no puedo participar en el juego actualmente, por favor contacte con el equipo de atención al cliente.</t>
+  </si>
+  <si>
+    <t>अकाउंट में गड़बड़ी है, अभी गेम में हिस्सा नहीं ले पा रहे हैं, कृपया CS टीम से संपर्क करें</t>
+  </si>
+  <si>
+    <t>Terjadi anomali pada akun, saat ini tidak dapat berpartisipasi dalam permainan, silakan hubungi tim layanan pelanggan.</t>
+  </si>
+  <si>
+    <t>Anomalia na conta, impossibilitada de participar no jogo no momento. Entre em contacto com a equipa de suporte.</t>
+  </si>
+  <si>
+    <t>เกิดความผิดปกติของบัญชี ไม่สามารถเข้าร่วมเล่นเกมได้ในขณะนี้ โปรดติดต่อทีมบริการลูกค้า</t>
+  </si>
+  <si>
+    <t>Hesap anormalliği nedeniyle şu anda oyuna katılamıyorum, lütfen müşteri hizmetleri ekibiyle iletişime geçin.</t>
+  </si>
+  <si>
+    <t>اکاؤنٹ میں بے ضابطگی، فی الحال گیم میں حصہ لینے سے قاصر، براہ کرم CS ٹیم سے رابطہ کریں۔</t>
+  </si>
+  <si>
+    <t>Anomalya sa account, hindi makasali sa laro sa kasalukuyan, mangyaring makipag-ugnayan sa CS team</t>
+  </si>
+  <si>
     <t>common_bet</t>
   </si>
   <si>
@@ -545,82 +1049,108 @@
     <t>common_rule_content</t>
   </si>
   <si>
-    <t>1. 选择您的金额并选择摩天轮上的食物进行押注；
-2. 押注时间结束则开始开奖，如果开奖结果与你押注选项一致，您将根据图标上的倍率获得对应奖励；
-3.还有几率抽中2个大奖： 如果公布的是“沙拉”，则所有蔬菜都将获得奖励； 
-如果公布的是“披萨”，则所有肉类都将获得奖励。</t>
-  </si>
-  <si>
-    <t>1. Select your cost amount and choose food items on the Ferris wheel to place your cost;
-2. The cost period ends, and the draw begins. If the result matches your cost, you will receive the corresponding reward based on the multiplier shown on the icon;
-3. There is also a chance to win two grand prizes: If the announced prize is "Salad," all vegetables will be awarded; 
-If the announced prize is "Pizza," all meats will be awarded.</t>
-  </si>
-  <si>
-    <t>١. حدد مبلغ رهانك واختر أصناف الطعام على عجلة فيريس لوضع رهانك؛
-٢. تنتهي فترة الرهان، ويبدأ السحب. إذا تطابقت النتيجة مع رهانك، فستحصل على الجائزة المناسبة بناءً على المضاعف الموضح على الأيقونة؛
-٣. هناك أيضًا فرصة للفوز بجائزتين كبيرتين: إذا كانت الجائزة المعلنة هي "سلطة"، فستحصل على جميع الخضراوات؛
-إذا كانت الجائزة المعلنة هي "بيتزا"، فستحصل على جميع أنواع اللحوم.</t>
-  </si>
-  <si>
-    <t>1. Chọn số tiền đặt cược và chọn các món ăn trên vòng quay để đặt cược;
-2. Thời gian đặt cược kết thúc và bắt đầu quay thưởng. Nếu kết quả trùng khớp với số tiền đặt cược, bạn sẽ nhận được phần thưởng tương ứng dựa trên hệ số nhân hiển thị trên biểu tượng;
-3. Ngoài ra còn có cơ hội trúng hai giải thưởng lớn: Nếu giải thưởng được công bố là "Salad", bạn sẽ nhận được tất cả các loại rau;
-Nếu giải thưởng được công bố là "Pizza", bạn sẽ nhận được tất cả các loại thịt.</t>
-  </si>
-  <si>
-    <t>১. আপনার বাজি ধরার পরিমাণ নির্বাচন করুন এবং বাজি রাখার জন্য ফেরিস হুইল থেকে খাবারের আইটেম বেছে নিন;
-২. বাজি ধরার সময়সীমা শেষ হলে ড্র শুরু হবে। ফলাফল আপনার বাজির সাথে মিলে গেলে, আইকনে দেখানো মাল্টিপ্লায়ার অনুযায়ী আপনি পুরস্কার পাবেন;
-৩. দুটি গ্র্যান্ড প্রাইজ জেতারও সুযোগ রয়েছে: ঘোষিত পুরস্কার "সালাদ" হলে, সমস্ত সবজি পুরস্কার হিসেবে দেওয়া হবে;
-ঘোষিত পুরস্কার "পিজ্জা" হলে, সমস্ত মাংস পুরস্কার হিসেবে দেওয়া হবে।</t>
-  </si>
-  <si>
-    <t>1. Selecciona el monto de tu apuesta y elige los alimentos en la noria para realizarla.
-2. El plazo de apuestas finaliza y comienza el sorteo. Si el resultado coincide con tu apuesta, recibirás el premio correspondiente según el multiplicador que aparece en el icono.
-3. También tienes la oportunidad de ganar dos grandes premios: Si el premio anunciado es "Ensalada", recibirás todas las verduras;
-Si el premio anunciado es "Pizza", recibirás todas las carnes.</t>
-  </si>
-  <si>
-    <t>1. अपनी बेट की रकम चुनें और बेट लगाने के लिए फेरिस व्हील पर खाने की चीज़ें चुनें;
-2. बेट का समय खत्म होता है, और ड्रॉ शुरू होता है। अगर नतीजा आपकी बेट से मैच करता है, तो आपको आइकन पर दिखाए गए मल्टीप्लायर के आधार पर उसी हिसाब का इनाम मिलेगा;
-3. दो बड़े इनाम जीतने का भी मौका है: अगर बताया गया इनाम "सलाद" है, तो सभी सब्ज़ियाँ इनाम में दी जाएँगी;
-अगर बताया गया इनाम "पिज़्ज़ा" है, तो सभी मीट इनाम में दिए जाएँगे।</t>
-  </si>
-  <si>
-    <t>1. Pilih jumlah taruhan Anda dan pilih makanan di kincir ria untuk memasang taruhan Anda;
-2. Periode taruhan berakhir, dan pengundian dimulai. Jika hasilnya sesuai dengan taruhan Anda, Anda akan menerima hadiah yang sesuai berdasarkan pengali yang ditampilkan pada ikon;
-3. Ada juga kesempatan untuk memenangkan dua hadiah utama: Jika hadiah yang diumumkan adalah Salad, semua sayuran akan diberikan;
-Jika hadiah yang diumumkan adalah "Pizza," semua daging akan diberikan.</t>
-  </si>
-  <si>
-    <t>1.º Selecione o valor da sua aposta e escolha os itens alimentares na roda gigante para apostar;
-2.º O período da aposta termina e o sorteio começa. Se o resultado corresponder à sua aposta, receberá a recompensa correspondente com base no multiplicador apresentado no ícone;
-3.º Existe ainda a hipótese de ganhar dois grandes prémios: Se o prémio anunciado for "Salada", todos os legumes serão premiados;
-Se o prémio anunciado for "Pizza", todas as carnes serão premiadas.</t>
-  </si>
-  <si>
-    <t>1. เลือกจำนวนเงินเดิมพันและเลือกรายการอาหารบนชิงช้าสวรรค์เพื่อวางเดิมพัน
-2. เมื่อระยะเวลาการเดิมพันสิ้นสุดลง การจับรางวัลจะเริ่มต้นขึ้น หากผลลัพธ์ตรงกับการเดิมพันของคุณ คุณจะได้รับรางวัลตามตัวคูณที่แสดงบนไอคอน
-3. นอกจากนี้ยังมีโอกาสลุ้นรับรางวัลใหญ่สองรางวัล: หากรางวัลที่ประกาศคือ "สลัด" คุณจะได้รับผักทั้งหมด
-หากรางวัลที่ประกาศคือ "พิซซ่า" คุณจะได้รับเนื้อสัตว์ทั้งหมด</t>
-  </si>
-  <si>
-    <t>1. Bahis miktarınızı seçin ve bahsinizi koymak için dönme dolaptaki yiyeceklerden birini seçin;
-2. Bahis süresi sona erer ve çekiliş başlar. Sonuç bahsinizle eşleşirse, simgede gösterilen çarpana göre ilgili ödülü alırsınız;
-3. Ayrıca iki büyük ödül kazanma şansı da vardır: Açıklanan ödül "Salata" ise, tüm sebzeler verilecektir;
-Açıklanan ödül "Pizza" ise, tüm etler verilecektir.</t>
-  </si>
-  <si>
-    <t>1. اپنی شرط کی رقم منتخب کریں اور اپنی شرط لگانے کے لیے فیرس وہیل پر کھانے کی اشیاء کا انتخاب کریں۔
-2. شرط کی مدت ختم ہوتی ہے، اور قرعہ اندازی شروع ہوتی ہے۔ اگر نتیجہ آپ کی شرط سے ملتا ہے، تو آپ کو آئیکن پر دکھائے گئے ضرب کی بنیاد پر متعلقہ انعام ملے گا۔
-3. دو عظیم الشان انعامات جیتنے کا بھی موقع ہے: اگر اعلان کردہ انعام "سلاد ہے تو تمام سبزیاں دی جائیں گی۔
-اگر اعلان کردہ انعام ""پیزا،" ہے تو تمام گوشت سے نوازا جائے گا۔</t>
-  </si>
-  <si>
-    <t>1. Piliin ang halaga ng iyong taya at pumili ng mga pagkain sa Ferris wheel para ilagay ang iyong taya;
-2. Magtatapos ang panahon ng taya, at magsisimula ang bunutan. Kung ang resulta ay tumutugma sa iyong taya, matatanggap mo ang kaukulang gantimpala batay sa multiplier na ipinapakita sa icon;
-3. Mayroon ding pagkakataong manalo ng dalawang malalaking premyo: Kung ang inanunsyong premyo ay "Salad," lahat ng gulay ay igagawad;
-Kung ang inanunsyong premyo ay "Pizza," lahat ng karne ay igagawad.</t>
+    <t>1. 选择您的投注金额，并选择要投注的食物；
+2. 每一轮的投注时间为 20 秒，之后结果会立即公布。
+3. 如果所公布的结果与您所选择的食物相符，您将按照相应的概率获得相应的奖励；
+4. 随着更多用户参与游戏，官方的奖金池将会增加。当奖金池达到一定数额时，就会有“披萨”或“沙拉”等奖励可供领取。
+5. 如果宣布“沙拉”菜品，那么所有蔬菜都将获得奖励；
+6. 如果宣布“披萨”这一菜品，那么所有的肉类菜品都将获得奖励。</t>
+  </si>
+  <si>
+    <t>1. Choose your bet amount and select the food to bet;
+2. There're 20 seconds for betting each round, the result will be announced instantly afterwards;
+3. If the result announced matches the food you have selected, you will rewards relative to the respective odds;
+4. The official prize pool will increase as more users participate in game, there will be a chance for "PIZZA" or "SALAD" reward as prize pool reaches a certain amount;
+5. If "SALAD" was announced, then all vegetables will be rewarded;
+6. If "PIZZA" was announced, then all meats will be rewarded.</t>
+  </si>
+  <si>
+    <t>١. حدد مبلغ رهانك واختر الطعام الذي ترغب بالمراهنة عليه؛
+٢. لديك ٢٠ ثانية للمراهنة في كل جولة، وسيتم إعلان النتيجة فورًا بعد ذلك؛
+٣. إذا تطابقت النتيجة المعلنة مع الطعام الذي اخترته، فستحصل على مكافآت تتناسب مع احتمالات الفوز؛
+٤. سيزداد مجموع الجوائز الرسمي مع ازدياد عدد المشاركين في اللعبة، وستكون هناك فرصة للفوز بجائزة "بيتزا" أو "سلطة" عند وصول مجموع الجوائز إلى مبلغ معين؛
+٥. إذا تم الإعلان عن "سلطة"، فستحصل على مكافأة تشمل جميع أنواع الخضراوات؛
+٦. إذا تم الإعلان عن "بيتزا"، فستحصل على مكافأة تشمل جميع أنواع اللحوم.</t>
+  </si>
+  <si>
+    <t>1. Chọn số tiền đặt cược và chọn món ăn bạn muốn đặt cược;
+2. Mỗi vòng có 20 giây để đặt cược, kết quả sẽ được công bố ngay lập tức sau đó;
+3. Nếu kết quả được công bố trùng khớp với món ăn bạn đã chọn, bạn sẽ nhận được phần thưởng tương ứng với tỷ lệ cược;
+4. Tổng giải thưởng sẽ tăng lên khi có nhiều người chơi tham gia trò chơi, sẽ có cơ hội nhận được phần thưởng "PIZZA" hoặc "SALAD" khi tổng giải thưởng đạt đến một mức nhất định;
+5. Nếu kết quả là "SALAD", bạn sẽ nhận được phần thưởng là tất cả các loại rau;
+6. Nếu kết quả là "PIZZA", bạn sẽ nhận được phần thưởng là tất cả các loại thịt.</t>
+  </si>
+  <si>
+    <t>১. আপনার বাজি ধরার পরিমাণ এবং বাজি ধরার জন্য খাবার নির্বাচন করুন;
+২. প্রতিটি রাউন্ডে বাজি ধরার জন্য ২০ সেকেন্ড সময় থাকবে, এরপরেই ফলাফল তাৎক্ষণিকভাবে ঘোষণা করা হবে;
+৩. ঘোষিত ফলাফল আপনার নির্বাচিত খাবারের সাথে মিলে গেলে, আপনি সংশ্লিষ্ট বাজির দর অনুযায়ী পুরস্কার পাবেন;
+৪. গেমে যত বেশি ব্যবহারকারী অংশগ্রহণ করবে, অফিসিয়াল প্রাইজ পুল তত বাড়বে, প্রাইজ পুল একটি নির্দিষ্ট পরিমাণে পৌঁছালে "পিজ্জা" বা "সালাদ" পুরস্কার পাওয়ার সুযোগ থাকবে;
+৫. যদি "সালাদ" ঘোষণা করা হয়, তাহলে সমস্ত সবজি পুরস্কার হিসেবে দেওয়া হবে;
+৬. যদি "পিজ্জা" ঘোষণা করা হয়, তাহলে সমস্ত মাংস পুরস্কার হিসেবে দেওয়া হবে।</t>
+  </si>
+  <si>
+    <t>1. Elige el monto de tu apuesta y selecciona el alimento por el que apostar;
+2. Tienes 20 segundos para apostar en cada ronda; el resultado se anunciará inmediatamente después;
+3. Si el resultado anunciado coincide con el alimento que seleccionaste, recibirás una recompensa proporcional a las probabilidades;
+4. El premio acumulado aumentará a medida que más usuarios participen en el juego. Al alcanzar cierto monto, tendrás la oportunidad de ganar una "PIZZA" o una "ENSALADA";
+5. Si se anuncia "ENSALADA", se premiarán todas las verduras;
+6. Si se anuncia "PIZZA", se premiarán todas las carnes.</t>
+  </si>
+  <si>
+    <t>1. अपनी बेट की रकम चुनें और बेट लगाने के लिए खाना चुनें;
+2. हर राउंड में बेट लगाने के लिए 20 सेकंड होते हैं, उसके तुरंत बाद रिज़ल्ट बताया जाएगा;
+3. अगर बताया गया रिज़ल्ट आपके चुने हुए खाने से मैच करता है, तो आपको संबंधित ऑड्स के हिसाब से रिवॉर्ड मिलेंगे;
+4. जैसे-जैसे ज़्यादा यूज़र्स गेम में हिस्सा लेंगे, ऑफिशियल प्राइज़ पूल बढ़ेगा, प्राइज़ पूल के एक तय रकम तक पहुँचने पर "PIZZA" या "SALAD" रिवॉर्ड का मौका मिलेगा;
+5. अगर "SALAD" बताया गया है, तो सभी सब्ज़ियों को रिवॉर्ड दिया जाएगा;
+6. अगर "PIZZA" बताया गया है, तो सभी मीट को रिवॉर्ड दिया जाएगा।</t>
+  </si>
+  <si>
+    <t>1. Pilih jumlah taruhan Anda dan pilih makanan yang ingin Anda pertaruhkan;
+2. Ada waktu 20 detik untuk bertaruh di setiap putaran, hasilnya akan diumumkan secara instan setelahnya;
+3. Jika hasil yang diumumkan sesuai dengan makanan yang Anda pilih, Anda akan mendapatkan hadiah yang sesuai dengan peluangnya;
+4. Total hadiah resmi akan meningkat seiring bertambahnya jumlah pengguna yang berpartisipasi dalam permainan, akan ada kesempatan untuk mendapatkan hadiah "PIZZA" atau "SALAD" ketika total hadiah mencapai jumlah tertentu;
+5. Jika "SALAD" diumumkan, maka semua sayuran akan mendapatkan hadiah;
+6. Jika "PIZZA" diumumkan, maka semua daging akan mendapatkan hadiah.</t>
+  </si>
+  <si>
+    <t>1.º Escolha o valor da sua aposta e selecione o alimento em que pretende apostar;
+2.º Terá 20 segundos para apostar em cada ronda e o resultado será anunciado imediatamente a seguir;
+3.Se o resultado anunciado corresponder ao alimento que selecionou, receberá uma recompensa proporcional às respetivas probabilidades;
+4.º O prémio total aumentará à medida que mais utilizadores participarem no jogo. Haverá uma hipótese de ganhar uma "PIZZA" ou uma "SALADA" como prémio quando o prémio total atingir um determinado valor;
+5.Se o resultado anunciado for "SALADA", todos os legumes serão premiados;
+6.Se o resultado anunciado for "PIZZA", todas as carnes serão premiadas.</t>
+  </si>
+  <si>
+    <t>1. เลือกจำนวนเงินเดิมพันและเลือกอาหารที่จะเดิมพัน
+2. แต่ละรอบมีเวลา 20 วินาทีสำหรับการเดิมพัน ผลจะประกาศทันทีหลังจากนั้น
+3. หากผลที่ประกาศตรงกับอาหารที่คุณเลือก คุณจะได้รับรางวัลตามอัตราต่อรองที่กำหนด
+4. เงินรางวัลรวมจะเพิ่มขึ้นเมื่อมีผู้เล่นเข้าร่วมเกมมากขึ้น และจะมีโอกาสได้รับรางวัล "พิซซ่า" หรือ "สลัด" เมื่อเงินรางวัลรวมถึงจำนวนที่กำหนด
+5. หากประกาศ "สลัด" จะได้รับรางวัลเป็นผักทุกชนิด
+6. หากประกาศ "พิซซ่า" จะได้รับรางวัลเป็นเนื้อสัตว์ทุกชนิด</t>
+  </si>
+  <si>
+    <t>1. Bahis miktarınızı seçin ve bahis yapacağınız yemeği belirleyin;
+2. Her tur için 20 saniye bahis süreniz var, sonuç hemen ardından açıklanacak;
+3. Açıklanan sonuç seçtiğiniz yemekle eşleşirse, ilgili oranlara göre ödül kazanacaksınız;
+4. Oyuna daha fazla kullanıcı katıldıkça resmi ödül havuzu artacak, ödül havuzu belirli bir miktara ulaştığında "PİZZA" veya "SALATA" ödülü kazanma şansı olacak;
+5. "SALATA" açıklanırsa, tüm sebzeler ödüllendirilecek;
+6. "PİZZA" açıklanırsa, tüm etler ödüllendirilecek.</t>
+  </si>
+  <si>
+    <t>1. اپنی شرط کی رقم کا انتخاب کریں اور شرط لگانے کے لیے کھانا منتخب کریں۔
+2. ہر راؤنڈ میں شرط لگانے کے لیے 20 سیکنڈ ہوتے ہیں، نتیجہ کا اعلان فوراً بعد کیا جائے گا۔
+3. اگر اعلان کردہ نتیجہ آپ کے منتخب کردہ کھانے سے میل کھاتا ہے، تو آپ کو متعلقہ مشکلات کے مطابق انعامات ملیں گے۔
+4. باضابطہ انعامی پول بڑھے گا کیونکہ زیادہ سے زیادہ صارفین گیم میں حصہ لیں گے، انعامی پول ایک مخصوص رقم تک پہنچنے پر "PIZZA" یا "SALAD" انعام کا موقع ملے گا۔
+5. اگر "سلاد" کا اعلان کیا گیا تو تمام سبزیوں کو انعام دیا جائے گا۔
+6. اگر "PIZZA" کا اعلان کیا گیا تھا، تو تمام گوشت کو انعام دیا جائے گا۔</t>
+  </si>
+  <si>
+    <t>1. Piliin ang halaga ng iyong taya at piliin ang pagkain na tatayaan;
+2. May 20 segundo para sa pagtaya sa bawat round, ang resulta ay iaanunsyo kaagad pagkatapos;
+3. Kung ang resultang inanunsyo ay tumutugma sa pagkain na iyong napili, makakatanggap ka ng mga gantimpala kaugnay ng kani-kanilang logro;
+4. Ang opisyal na premyo ay tataas habang mas maraming user ang lumahok sa laro, magkakaroon ng pagkakataon para sa gantimpalang "PIZZA" o "SALAD" kapag umabot sa isang tiyak na halaga ang premyo;
+5. Kung ang "SALAD" ay inanunsyo, lahat ng gulay ay gagantimpalaan;
+6. Kung ang "PIZZA" ay inanunsyo, lahat ng karne ay gagantimpalaan.</t>
   </si>
   <si>
     <t>common_history</t>
@@ -1135,7 +1665,7 @@
     <t>今天赢得</t>
   </si>
   <si>
-    <t>Prize today</t>
+    <t>Game History</t>
   </si>
   <si>
     <t>جائزة اليوم</t>
@@ -1467,12 +1997,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1827,7 +2363,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
@@ -1851,16 +2387,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="8">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="9">
@@ -1869,109 +2405,121 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="10">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2305,7 +2853,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N112"/>
+  <dimension ref="A1:N123"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="28.1333333333333" style="2" customWidth="1"/>
@@ -2563,2500 +3111,2984 @@
         <v>40</v>
       </c>
       <c r="J6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K6" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="L6" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="M6" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="M6" s="6" t="s">
+      <c r="N6" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:14">
       <c r="A7" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>47</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>47</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:14">
-      <c r="A8" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K8" s="6" t="s">
+      <c r="A8" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="B8" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="M8" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="N8" s="6" t="s">
+      <c r="C8" s="8" t="s">
         <v>60</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:14">
       <c r="A9" s="5" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="10" customFormat="1" spans="1:14">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:14">
       <c r="A10" s="7" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="43.5" spans="1:14">
       <c r="A11" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="L11" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="M11" s="8" t="s">
+      <c r="B11" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="N11" s="8" t="s">
+      <c r="C11" s="9" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="7" t="s">
+      <c r="D11" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="E11" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="F11" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="G11" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="H11" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="I11" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="J11" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="K11" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="L11" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="J12" s="8" t="s">
+      <c r="M11" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="N11" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="L12" s="8" t="s">
+    </row>
+    <row r="12" s="1" customFormat="1" ht="46.5" spans="1:14">
+      <c r="A12" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="M12" s="8" t="s">
+      <c r="B12" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="N12" s="8" t="s">
+      <c r="C12" s="10" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="13" customFormat="1" spans="1:14">
+      <c r="D12" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="L12" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="M12" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="N12" s="10" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="56" customHeight="1" spans="1:14">
       <c r="A13" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="M13" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="N13" s="8" t="s">
+      <c r="B13" s="9" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="7" t="s">
+      <c r="C13" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="D13" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="E13" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="F13" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="G13" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="H13" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="I13" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="J13" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="K13" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="L13" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="K14" s="8" t="s">
+      <c r="M13" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="L14" s="8" t="s">
+      <c r="N13" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="M14" s="8" t="s">
+    </row>
+    <row r="14" s="1" customFormat="1" ht="49.5" spans="1:14">
+      <c r="A14" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="N14" s="8" t="s">
+      <c r="B14" s="6" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="7" t="s">
+      <c r="C14" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="D14" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="E14" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="F14" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="G14" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="H14" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="I14" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="J14" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="K14" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="J15" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="K15" s="8" t="s">
+      <c r="L14" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="L15" s="8" t="s">
+      <c r="M14" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="M15" s="8" t="s">
+      <c r="N14" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="N15" s="8" t="s">
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:14">
+      <c r="A15" s="5" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="C15" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="D15" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="E15" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="F15" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="G15" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="H15" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="I15" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="I16" s="8" t="s">
+      <c r="J15" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="J16" s="8" t="s">
+      <c r="K15" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="K16" s="8" t="s">
+      <c r="L15" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="L16" s="8" t="s">
+      <c r="M15" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="M16" s="8" t="s">
+      <c r="N15" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="N16" s="8" t="s">
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:14">
+      <c r="A16" s="5" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="17" customFormat="1" ht="202" customHeight="1" spans="1:14">
-      <c r="A17" s="9" t="s">
+      <c r="B16" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="C16" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="D16" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="E16" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="F16" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="G16" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="G17" s="10" t="s">
+      <c r="H16" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="H17" s="10" t="s">
+      <c r="I16" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="I17" s="10" t="s">
+      <c r="J16" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="J17" s="10" t="s">
+      <c r="K16" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="K17" s="10" t="s">
+      <c r="L16" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="L17" s="10" t="s">
+      <c r="M16" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="M17" s="10" t="s">
+      <c r="N16" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="N17" s="10" t="s">
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:14">
+      <c r="A17" s="5" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="C17" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="N17" s="6" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:14">
+      <c r="A18" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="B18" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="C18" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="D18" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="E18" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="F18" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="G18" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="I18" s="8" t="s">
+      <c r="H18" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="J18" s="8" t="s">
+      <c r="I18" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="K18" s="8" t="s">
+      <c r="J18" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="L18" s="8" t="s">
+      <c r="K18" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="M18" s="8" t="s">
+      <c r="L18" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="N18" s="8" t="s">
+      <c r="M18" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="N18" s="6" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="19" ht="33" spans="1:14">
-      <c r="A19" s="7" t="s">
+    <row r="19" s="1" customFormat="1" spans="1:14">
+      <c r="A19" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F19" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="G19" s="11" t="s">
+      <c r="G19" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="H19" s="11" t="s">
+      <c r="H19" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="I19" s="11" t="s">
+      <c r="I19" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="J19" s="11" t="s">
+      <c r="J19" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="K19" s="11" t="s">
+      <c r="K19" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="L19" s="11" t="s">
+      <c r="L19" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="M19" s="11" t="s">
+      <c r="M19" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="N19" s="11" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20" s="7" t="s">
+      <c r="N19" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="B20" s="8" t="s">
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:14">
+      <c r="A20" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="B20" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="C20" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="D20" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="E20" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="F20" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="G20" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="I20" s="8" t="s">
+      <c r="H20" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="J20" s="8" t="s">
+      <c r="I20" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="K20" s="8" t="s">
+      <c r="J20" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="L20" s="8" t="s">
+      <c r="K20" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="M20" s="8" t="s">
+      <c r="L20" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="N20" s="8" t="s">
+      <c r="M20" s="6" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" s="7" t="s">
+      <c r="N20" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="B21" s="8" t="s">
+    </row>
+    <row r="21" customFormat="1" spans="1:14">
+      <c r="A21" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="B21" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="C21" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="D21" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="E21" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="F21" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="G21" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="H21" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="J21" s="8" t="s">
+      <c r="I21" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="K21" s="8" t="s">
+      <c r="J21" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="L21" s="8" t="s">
+      <c r="K21" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="M21" s="8" t="s">
+      <c r="L21" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="N21" s="8" t="s">
+      <c r="M21" s="12" t="s">
         <v>239</v>
       </c>
+      <c r="N21" s="12" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="B22" s="8" t="s">
+      <c r="A22" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="B22" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="C22" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="D22" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="E22" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="F22" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="G22" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="I22" s="8" t="s">
+      <c r="H22" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="J22" s="8" t="s">
+      <c r="I22" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="K22" s="8" t="s">
+      <c r="J22" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="L22" s="8" t="s">
+      <c r="K22" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="M22" s="8" t="s">
+      <c r="L22" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="N22" s="8" t="s">
+      <c r="M22" s="12" t="s">
         <v>253</v>
       </c>
+      <c r="N22" s="12" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="B23" s="8" t="s">
+      <c r="A23" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="B23" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="C23" s="12" t="s">
         <v>257</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="D23" s="12" t="s">
         <v>258</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="E23" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="F23" s="12" t="s">
         <v>260</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="G23" s="12" t="s">
         <v>261</v>
       </c>
-      <c r="I23" s="8" t="s">
+      <c r="H23" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="J23" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="K23" s="8" t="s">
+      <c r="I23" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="L23" s="8" t="s">
+      <c r="J23" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="M23" s="8" t="s">
+      <c r="K23" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="N23" s="8" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
-      <c r="A24" s="7" t="s">
+      <c r="L23" s="12" t="s">
         <v>266</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="M23" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="N23" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="D24" s="8" t="s">
+    </row>
+    <row r="24" customFormat="1" spans="1:14">
+      <c r="A24" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="B24" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="C24" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="D24" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="E24" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="I24" s="8" t="s">
+      <c r="F24" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="J24" s="8" t="s">
+      <c r="G24" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="K24" s="8" t="s">
+      <c r="H24" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="L24" s="8" t="s">
+      <c r="I24" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="M24" s="8" t="s">
+      <c r="J24" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="K24" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="N24" s="8" t="s">
+      <c r="L24" s="12" t="s">
         <v>279</v>
       </c>
+      <c r="M24" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="N24" s="12" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="C25" s="8" t="s">
+      <c r="A25" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="B25" s="12" t="s">
         <v>283</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="C25" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="D25" s="12" t="s">
         <v>285</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="E25" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="F25" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="I25" s="8" t="s">
+      <c r="G25" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="J25" s="8" t="s">
+      <c r="H25" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="K25" s="8" t="s">
+      <c r="I25" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="L25" s="8" t="s">
+      <c r="J25" s="12" t="s">
         <v>291</v>
       </c>
-      <c r="M25" s="8" t="s">
+      <c r="K25" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="N25" s="8" t="s">
+      <c r="L25" s="12" t="s">
         <v>293</v>
       </c>
+      <c r="M25" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="N25" s="12" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="C26" s="8" t="s">
+      <c r="A26" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="B26" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="C26" s="12" t="s">
         <v>298</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="D26" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="E26" s="12" t="s">
         <v>300</v>
       </c>
-      <c r="H26" s="8" t="s">
+      <c r="F26" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="I26" s="8" t="s">
+      <c r="G26" s="12" t="s">
         <v>302</v>
       </c>
-      <c r="J26" s="8" t="s">
+      <c r="H26" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="K26" s="8" t="s">
+      <c r="I26" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="L26" s="8" t="s">
+      <c r="J26" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="K26" s="12" t="s">
         <v>305</v>
       </c>
-      <c r="M26" s="8" t="s">
+      <c r="L26" s="12" t="s">
         <v>306</v>
       </c>
-      <c r="N26" s="8" t="s">
+      <c r="M26" s="12" t="s">
         <v>307</v>
       </c>
+      <c r="N26" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="B27" s="8" t="s">
+      <c r="A27" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="B27" s="12" t="s">
         <v>310</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="C27" s="12" t="s">
         <v>311</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="D27" s="12" t="s">
         <v>312</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="E27" s="12" t="s">
         <v>313</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="F27" s="12" t="s">
         <v>314</v>
       </c>
-      <c r="H27" s="8" t="s">
+      <c r="G27" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="I27" s="8" t="s">
+      <c r="H27" s="12" t="s">
         <v>316</v>
       </c>
-      <c r="J27" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="K27" s="8" t="s">
+      <c r="I27" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="L27" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="M27" s="8" t="s">
+      <c r="J27" s="12" t="s">
         <v>318</v>
       </c>
-      <c r="N27" s="8" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
-      <c r="A28" s="7" t="s">
+      <c r="K27" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="L27" s="12" t="s">
         <v>320</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="M27" s="12" t="s">
         <v>321</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="N27" s="12" t="s">
         <v>322</v>
       </c>
-      <c r="E28" s="8" t="s">
+    </row>
+    <row r="28" ht="202" customHeight="1" spans="1:14">
+      <c r="A28" s="13" t="s">
         <v>323</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="B28" s="14" t="s">
         <v>324</v>
       </c>
-      <c r="G28" s="8" t="s">
+      <c r="C28" s="14" t="s">
         <v>325</v>
       </c>
-      <c r="H28" s="8" t="s">
+      <c r="D28" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="I28" s="8" t="s">
+      <c r="E28" s="14" t="s">
         <v>327</v>
       </c>
-      <c r="J28" s="8" t="s">
+      <c r="F28" s="14" t="s">
         <v>328</v>
       </c>
-      <c r="K28" s="8" t="s">
+      <c r="G28" s="14" t="s">
         <v>329</v>
       </c>
-      <c r="L28" s="8" t="s">
+      <c r="H28" s="14" t="s">
         <v>330</v>
       </c>
-      <c r="M28" s="8" t="s">
+      <c r="I28" s="14" t="s">
         <v>331</v>
       </c>
-      <c r="N28" s="8" t="s">
+      <c r="J28" s="14" t="s">
         <v>332</v>
       </c>
+      <c r="K28" s="14" t="s">
+        <v>333</v>
+      </c>
+      <c r="L28" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="M28" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="N28" s="14" t="s">
+        <v>336</v>
+      </c>
     </row>
     <row r="29" spans="1:14">
-      <c r="A29" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="F29" s="8" t="s">
+      <c r="A29" s="11" t="s">
         <v>337</v>
       </c>
-      <c r="G29" s="8" t="s">
+      <c r="B29" s="12" t="s">
         <v>338</v>
       </c>
-      <c r="H29" s="8" t="s">
+      <c r="C29" s="12" t="s">
         <v>339</v>
       </c>
-      <c r="I29" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="J29" s="8" t="s">
+      <c r="D29" s="12" t="s">
         <v>340</v>
       </c>
-      <c r="K29" s="8" t="s">
+      <c r="E29" s="12" t="s">
         <v>341</v>
       </c>
-      <c r="L29" s="8" t="s">
+      <c r="F29" s="12" t="s">
         <v>342</v>
       </c>
-      <c r="M29" s="8" t="s">
+      <c r="G29" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="N29" s="8" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
-      <c r="A30" s="7" t="s">
+      <c r="H29" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="I29" s="12" t="s">
         <v>345</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="J29" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="K29" s="12" t="s">
         <v>347</v>
       </c>
-      <c r="E30" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="F30" s="8" t="s">
+      <c r="L29" s="12" t="s">
         <v>348</v>
       </c>
-      <c r="G30" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="H30" s="8" t="s">
+      <c r="M29" s="12" t="s">
         <v>349</v>
       </c>
-      <c r="I30" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="J30" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="K30" s="8" t="s">
+      <c r="N29" s="12" t="s">
         <v>350</v>
       </c>
-      <c r="L30" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="M30" s="8" t="s">
+    </row>
+    <row r="30" ht="33" spans="1:14">
+      <c r="A30" s="11" t="s">
         <v>351</v>
       </c>
-      <c r="N30" s="8" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="31" ht="16.5" spans="1:14">
-      <c r="A31" s="7" t="s">
+      <c r="B30" s="12" t="s">
         <v>352</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="C30" s="15" t="s">
         <v>353</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="D30" s="15" t="s">
         <v>354</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="E30" s="15" t="s">
         <v>355</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="F30" s="15" t="s">
         <v>356</v>
       </c>
-      <c r="F31" s="11" t="s">
+      <c r="G30" s="15" t="s">
         <v>357</v>
       </c>
-      <c r="G31" s="11" t="s">
+      <c r="H30" s="15" t="s">
         <v>358</v>
       </c>
-      <c r="H31" s="11" t="s">
+      <c r="I30" s="15" t="s">
         <v>359</v>
       </c>
-      <c r="I31" s="11" t="s">
+      <c r="J30" s="15" t="s">
         <v>360</v>
       </c>
-      <c r="J31" s="11" t="s">
+      <c r="K30" s="15" t="s">
         <v>361</v>
       </c>
-      <c r="K31" s="11" t="s">
+      <c r="L30" s="15" t="s">
         <v>362</v>
       </c>
-      <c r="L31" s="11" t="s">
+      <c r="M30" s="15" t="s">
         <v>363</v>
       </c>
-      <c r="M31" s="11" t="s">
+      <c r="N30" s="15" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="11" t="s">
         <v>364</v>
       </c>
-      <c r="N31" s="11" t="s">
+      <c r="B31" s="12" t="s">
         <v>365</v>
       </c>
+      <c r="C31" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="H31" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="I31" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="J31" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="K31" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="L31" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="M31" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="N31" s="12" t="s">
+        <v>377</v>
+      </c>
     </row>
     <row r="32" spans="1:14">
-      <c r="A32" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>369</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>370</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>372</v>
-      </c>
-      <c r="H32" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="I32" s="8" t="s">
-        <v>374</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="K32" s="8" t="s">
-        <v>376</v>
-      </c>
-      <c r="L32" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="M32" s="8" t="s">
+      <c r="A32" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="N32" s="8" t="s">
+      <c r="B32" s="12" t="s">
         <v>379</v>
       </c>
+      <c r="C32" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="G32" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="H32" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="I32" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="J32" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="K32" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="L32" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="M32" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="N32" s="12" t="s">
+        <v>391</v>
+      </c>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>381</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>383</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>384</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>385</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>386</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>388</v>
-      </c>
-      <c r="J33" s="8" t="s">
-        <v>389</v>
-      </c>
-      <c r="K33" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="L33" s="8" t="s">
-        <v>391</v>
-      </c>
-      <c r="M33" s="8" t="s">
+      <c r="A33" s="11" t="s">
         <v>392</v>
       </c>
-      <c r="N33" s="8" t="s">
+      <c r="B33" s="12" t="s">
         <v>393</v>
       </c>
+      <c r="C33" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>397</v>
+      </c>
+      <c r="G33" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="H33" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="I33" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="J33" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="K33" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="L33" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="M33" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="N33" s="12" t="s">
+        <v>405</v>
+      </c>
     </row>
     <row r="34" spans="1:14">
-      <c r="A34" s="12" t="s">
-        <v>394</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>395</v>
-      </c>
-      <c r="C34" s="13" t="s">
-        <v>396</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>397</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>398</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>399</v>
-      </c>
-      <c r="G34" s="13" t="s">
-        <v>400</v>
-      </c>
-      <c r="H34" s="13" t="s">
-        <v>401</v>
-      </c>
-      <c r="I34" s="13" t="s">
-        <v>402</v>
-      </c>
-      <c r="J34" s="13" t="s">
-        <v>403</v>
-      </c>
-      <c r="K34" s="13" t="s">
-        <v>404</v>
-      </c>
-      <c r="L34" s="13" t="s">
-        <v>405</v>
-      </c>
-      <c r="M34" s="13" t="s">
+      <c r="A34" s="11" t="s">
         <v>406</v>
       </c>
-      <c r="N34" s="13" t="s">
+      <c r="B34" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="C34" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>410</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="G34" s="12" t="s">
+        <v>412</v>
+      </c>
+      <c r="H34" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="I34" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="J34" s="12" t="s">
+        <v>412</v>
+      </c>
+      <c r="K34" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="L34" s="12" t="s">
+        <v>416</v>
+      </c>
+      <c r="M34" s="12" t="s">
+        <v>417</v>
+      </c>
+      <c r="N34" s="12" t="s">
+        <v>408</v>
+      </c>
     </row>
     <row r="35" spans="1:14">
-      <c r="A35" s="7"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="8"/>
-      <c r="J35" s="8"/>
-      <c r="K35" s="8"/>
-      <c r="L35" s="8"/>
-      <c r="M35" s="8"/>
-      <c r="N35" s="8"/>
+      <c r="A35" s="11" t="s">
+        <v>418</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>420</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>424</v>
+      </c>
+      <c r="H35" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="I35" s="12" t="s">
+        <v>426</v>
+      </c>
+      <c r="J35" s="12" t="s">
+        <v>427</v>
+      </c>
+      <c r="K35" s="12" t="s">
+        <v>428</v>
+      </c>
+      <c r="L35" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="M35" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="N35" s="12" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="36" spans="1:14">
-      <c r="A36" s="7"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="8"/>
-      <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="8"/>
-      <c r="M36" s="8"/>
-      <c r="N36" s="8"/>
+      <c r="A36" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>436</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="H36" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="I36" s="12" t="s">
+        <v>440</v>
+      </c>
+      <c r="J36" s="12" t="s">
+        <v>441</v>
+      </c>
+      <c r="K36" s="12" t="s">
+        <v>442</v>
+      </c>
+      <c r="L36" s="12" t="s">
+        <v>443</v>
+      </c>
+      <c r="M36" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="N36" s="12" t="s">
+        <v>445</v>
+      </c>
     </row>
     <row r="37" spans="1:14">
-      <c r="A37" s="7"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
-      <c r="I37" s="8"/>
-      <c r="J37" s="8"/>
-      <c r="K37" s="8"/>
-      <c r="L37" s="8"/>
-      <c r="M37" s="8"/>
-      <c r="N37" s="8"/>
+      <c r="A37" s="11" t="s">
+        <v>446</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>448</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>449</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>450</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>451</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>452</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>453</v>
+      </c>
+      <c r="I37" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>455</v>
+      </c>
+      <c r="K37" s="12" t="s">
+        <v>456</v>
+      </c>
+      <c r="L37" s="12" t="s">
+        <v>457</v>
+      </c>
+      <c r="M37" s="12" t="s">
+        <v>458</v>
+      </c>
+      <c r="N37" s="12" t="s">
+        <v>459</v>
+      </c>
     </row>
     <row r="38" spans="1:14">
-      <c r="A38" s="7"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="8"/>
-      <c r="I38" s="8"/>
-      <c r="J38" s="8"/>
-      <c r="K38" s="8"/>
-      <c r="L38" s="8"/>
-      <c r="M38" s="8"/>
-      <c r="N38" s="8"/>
+      <c r="A38" s="11" t="s">
+        <v>460</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>461</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>462</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>463</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>464</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>466</v>
+      </c>
+      <c r="H38" s="12" t="s">
+        <v>467</v>
+      </c>
+      <c r="I38" s="12" t="s">
+        <v>468</v>
+      </c>
+      <c r="J38" s="12" t="s">
+        <v>466</v>
+      </c>
+      <c r="K38" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="L38" s="12" t="s">
+        <v>468</v>
+      </c>
+      <c r="M38" s="12" t="s">
+        <v>470</v>
+      </c>
+      <c r="N38" s="12" t="s">
+        <v>462</v>
+      </c>
     </row>
     <row r="39" spans="1:14">
-      <c r="A39" s="7"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="8"/>
-      <c r="I39" s="8"/>
-      <c r="J39" s="8"/>
-      <c r="K39" s="8"/>
-      <c r="L39" s="8"/>
-      <c r="M39" s="8"/>
-      <c r="N39" s="8"/>
+      <c r="A39" s="11" t="s">
+        <v>471</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>472</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>473</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>474</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>475</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>476</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>477</v>
+      </c>
+      <c r="H39" s="12" t="s">
+        <v>478</v>
+      </c>
+      <c r="I39" s="12" t="s">
+        <v>479</v>
+      </c>
+      <c r="J39" s="12" t="s">
+        <v>480</v>
+      </c>
+      <c r="K39" s="12" t="s">
+        <v>481</v>
+      </c>
+      <c r="L39" s="12" t="s">
+        <v>482</v>
+      </c>
+      <c r="M39" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="N39" s="12" t="s">
+        <v>484</v>
+      </c>
     </row>
     <row r="40" spans="1:14">
-      <c r="A40" s="7"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="8"/>
-      <c r="I40" s="8"/>
-      <c r="J40" s="8"/>
-      <c r="K40" s="8"/>
-      <c r="L40" s="8"/>
-      <c r="M40" s="8"/>
-      <c r="N40" s="8"/>
+      <c r="A40" s="11" t="s">
+        <v>485</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>488</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>489</v>
+      </c>
+      <c r="G40" s="12" t="s">
+        <v>490</v>
+      </c>
+      <c r="H40" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="I40" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="J40" s="12" t="s">
+        <v>492</v>
+      </c>
+      <c r="K40" s="12" t="s">
+        <v>493</v>
+      </c>
+      <c r="L40" s="12" t="s">
+        <v>494</v>
+      </c>
+      <c r="M40" s="12" t="s">
+        <v>495</v>
+      </c>
+      <c r="N40" s="12" t="s">
+        <v>487</v>
+      </c>
     </row>
     <row r="41" spans="1:14">
-      <c r="A41" s="7"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="8"/>
-      <c r="I41" s="8"/>
-      <c r="J41" s="8"/>
-      <c r="K41" s="8"/>
-      <c r="L41" s="8"/>
-      <c r="M41" s="8"/>
-      <c r="N41" s="8"/>
-    </row>
-    <row r="42" spans="1:14">
-      <c r="A42" s="7"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8"/>
-      <c r="H42" s="8"/>
-      <c r="I42" s="8"/>
-      <c r="J42" s="8"/>
-      <c r="K42" s="8"/>
-      <c r="L42" s="8"/>
-      <c r="M42" s="8"/>
-      <c r="N42" s="8"/>
+      <c r="A41" s="11" t="s">
+        <v>496</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>497</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>498</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>499</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>498</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>500</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>498</v>
+      </c>
+      <c r="H41" s="12" t="s">
+        <v>501</v>
+      </c>
+      <c r="I41" s="12" t="s">
+        <v>498</v>
+      </c>
+      <c r="J41" s="12" t="s">
+        <v>498</v>
+      </c>
+      <c r="K41" s="12" t="s">
+        <v>502</v>
+      </c>
+      <c r="L41" s="12" t="s">
+        <v>498</v>
+      </c>
+      <c r="M41" s="12" t="s">
+        <v>503</v>
+      </c>
+      <c r="N41" s="12" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="42" ht="16.5" spans="1:14">
+      <c r="A42" s="11" t="s">
+        <v>504</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>505</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>507</v>
+      </c>
+      <c r="E42" s="15" t="s">
+        <v>508</v>
+      </c>
+      <c r="F42" s="15" t="s">
+        <v>509</v>
+      </c>
+      <c r="G42" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="H42" s="15" t="s">
+        <v>511</v>
+      </c>
+      <c r="I42" s="15" t="s">
+        <v>512</v>
+      </c>
+      <c r="J42" s="15" t="s">
+        <v>513</v>
+      </c>
+      <c r="K42" s="15" t="s">
+        <v>514</v>
+      </c>
+      <c r="L42" s="15" t="s">
+        <v>515</v>
+      </c>
+      <c r="M42" s="15" t="s">
+        <v>516</v>
+      </c>
+      <c r="N42" s="15" t="s">
+        <v>517</v>
+      </c>
     </row>
     <row r="43" spans="1:14">
-      <c r="A43" s="7"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="8"/>
-      <c r="I43" s="8"/>
-      <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
-      <c r="L43" s="8"/>
-      <c r="M43" s="8"/>
-      <c r="N43" s="8"/>
+      <c r="A43" s="11" t="s">
+        <v>518</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>519</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>520</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>521</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="F43" s="12" t="s">
+        <v>523</v>
+      </c>
+      <c r="G43" s="12" t="s">
+        <v>524</v>
+      </c>
+      <c r="H43" s="12" t="s">
+        <v>525</v>
+      </c>
+      <c r="I43" s="12" t="s">
+        <v>526</v>
+      </c>
+      <c r="J43" s="12" t="s">
+        <v>527</v>
+      </c>
+      <c r="K43" s="12" t="s">
+        <v>528</v>
+      </c>
+      <c r="L43" s="12" t="s">
+        <v>529</v>
+      </c>
+      <c r="M43" s="12" t="s">
+        <v>530</v>
+      </c>
+      <c r="N43" s="12" t="s">
+        <v>531</v>
+      </c>
     </row>
     <row r="44" spans="1:14">
-      <c r="A44" s="7"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="8"/>
-      <c r="H44" s="8"/>
-      <c r="I44" s="8"/>
-      <c r="J44" s="8"/>
-      <c r="K44" s="8"/>
-      <c r="L44" s="8"/>
-      <c r="M44" s="8"/>
-      <c r="N44" s="8"/>
+      <c r="A44" s="11" t="s">
+        <v>532</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>533</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>534</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>535</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>536</v>
+      </c>
+      <c r="F44" s="12" t="s">
+        <v>537</v>
+      </c>
+      <c r="G44" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="H44" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="I44" s="12" t="s">
+        <v>540</v>
+      </c>
+      <c r="J44" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="K44" s="12" t="s">
+        <v>542</v>
+      </c>
+      <c r="L44" s="12" t="s">
+        <v>543</v>
+      </c>
+      <c r="M44" s="12" t="s">
+        <v>544</v>
+      </c>
+      <c r="N44" s="12" t="s">
+        <v>545</v>
+      </c>
     </row>
     <row r="45" spans="1:14">
-      <c r="A45" s="7"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
-      <c r="I45" s="8"/>
-      <c r="J45" s="8"/>
-      <c r="K45" s="8"/>
-      <c r="L45" s="8"/>
-      <c r="M45" s="8"/>
-      <c r="N45" s="8"/>
+      <c r="A45" s="16" t="s">
+        <v>546</v>
+      </c>
+      <c r="B45" s="17" t="s">
+        <v>547</v>
+      </c>
+      <c r="C45" s="17" t="s">
+        <v>548</v>
+      </c>
+      <c r="D45" s="17" t="s">
+        <v>549</v>
+      </c>
+      <c r="E45" s="17" t="s">
+        <v>550</v>
+      </c>
+      <c r="F45" s="17" t="s">
+        <v>551</v>
+      </c>
+      <c r="G45" s="17" t="s">
+        <v>552</v>
+      </c>
+      <c r="H45" s="17" t="s">
+        <v>553</v>
+      </c>
+      <c r="I45" s="17" t="s">
+        <v>554</v>
+      </c>
+      <c r="J45" s="17" t="s">
+        <v>555</v>
+      </c>
+      <c r="K45" s="17" t="s">
+        <v>556</v>
+      </c>
+      <c r="L45" s="17" t="s">
+        <v>557</v>
+      </c>
+      <c r="M45" s="17" t="s">
+        <v>558</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>559</v>
+      </c>
     </row>
     <row r="46" spans="1:14">
-      <c r="A46" s="7"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="8"/>
-      <c r="I46" s="8"/>
-      <c r="J46" s="8"/>
-      <c r="K46" s="8"/>
-      <c r="L46" s="8"/>
-      <c r="M46" s="8"/>
-      <c r="N46" s="8"/>
+      <c r="A46" s="11"/>
+      <c r="B46" s="12"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="12"/>
+      <c r="K46" s="12"/>
+      <c r="L46" s="12"/>
+      <c r="M46" s="12"/>
+      <c r="N46" s="12"/>
     </row>
     <row r="47" spans="1:14">
-      <c r="A47" s="7"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
-      <c r="H47" s="8"/>
-      <c r="I47" s="8"/>
-      <c r="J47" s="8"/>
-      <c r="K47" s="8"/>
-      <c r="L47" s="8"/>
-      <c r="M47" s="8"/>
-      <c r="N47" s="8"/>
+      <c r="A47" s="11"/>
+      <c r="B47" s="12"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
+      <c r="I47" s="12"/>
+      <c r="J47" s="12"/>
+      <c r="K47" s="12"/>
+      <c r="L47" s="12"/>
+      <c r="M47" s="12"/>
+      <c r="N47" s="12"/>
     </row>
     <row r="48" spans="1:14">
-      <c r="A48" s="7"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="8"/>
-      <c r="H48" s="8"/>
-      <c r="I48" s="8"/>
-      <c r="J48" s="8"/>
-      <c r="K48" s="8"/>
-      <c r="L48" s="8"/>
-      <c r="M48" s="8"/>
-      <c r="N48" s="8"/>
+      <c r="A48" s="11"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="12"/>
+      <c r="I48" s="12"/>
+      <c r="J48" s="12"/>
+      <c r="K48" s="12"/>
+      <c r="L48" s="12"/>
+      <c r="M48" s="12"/>
+      <c r="N48" s="12"/>
     </row>
     <row r="49" spans="1:14">
-      <c r="A49" s="7"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
-      <c r="G49" s="8"/>
-      <c r="H49" s="8"/>
-      <c r="I49" s="8"/>
-      <c r="J49" s="8"/>
-      <c r="K49" s="8"/>
-      <c r="L49" s="8"/>
-      <c r="M49" s="8"/>
-      <c r="N49" s="8"/>
+      <c r="A49" s="11"/>
+      <c r="B49" s="12"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12"/>
+      <c r="H49" s="12"/>
+      <c r="I49" s="12"/>
+      <c r="J49" s="12"/>
+      <c r="K49" s="12"/>
+      <c r="L49" s="12"/>
+      <c r="M49" s="12"/>
+      <c r="N49" s="12"/>
     </row>
     <row r="50" spans="1:14">
-      <c r="A50" s="7"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="8"/>
-      <c r="H50" s="8"/>
-      <c r="I50" s="8"/>
-      <c r="J50" s="8"/>
-      <c r="K50" s="8"/>
-      <c r="L50" s="8"/>
-      <c r="M50" s="8"/>
-      <c r="N50" s="8"/>
+      <c r="A50" s="11"/>
+      <c r="B50" s="12"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12"/>
+      <c r="H50" s="12"/>
+      <c r="I50" s="12"/>
+      <c r="J50" s="12"/>
+      <c r="K50" s="12"/>
+      <c r="L50" s="12"/>
+      <c r="M50" s="12"/>
+      <c r="N50" s="12"/>
     </row>
     <row r="51" spans="1:14">
-      <c r="A51" s="7"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
-      <c r="G51" s="8"/>
-      <c r="H51" s="8"/>
-      <c r="I51" s="8"/>
-      <c r="J51" s="8"/>
-      <c r="K51" s="8"/>
-      <c r="L51" s="8"/>
-      <c r="M51" s="8"/>
-      <c r="N51" s="8"/>
+      <c r="A51" s="11"/>
+      <c r="B51" s="12"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="12"/>
+      <c r="G51" s="12"/>
+      <c r="H51" s="12"/>
+      <c r="I51" s="12"/>
+      <c r="J51" s="12"/>
+      <c r="K51" s="12"/>
+      <c r="L51" s="12"/>
+      <c r="M51" s="12"/>
+      <c r="N51" s="12"/>
     </row>
     <row r="52" spans="1:14">
-      <c r="A52" s="7"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="8"/>
-      <c r="H52" s="8"/>
-      <c r="I52" s="8"/>
-      <c r="J52" s="8"/>
-      <c r="K52" s="8"/>
-      <c r="L52" s="8"/>
-      <c r="M52" s="8"/>
-      <c r="N52" s="8"/>
+      <c r="A52" s="11"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
+      <c r="H52" s="12"/>
+      <c r="I52" s="12"/>
+      <c r="J52" s="12"/>
+      <c r="K52" s="12"/>
+      <c r="L52" s="12"/>
+      <c r="M52" s="12"/>
+      <c r="N52" s="12"/>
     </row>
     <row r="53" spans="1:14">
-      <c r="A53" s="7"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="8"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="8"/>
-      <c r="G53" s="8"/>
-      <c r="H53" s="8"/>
-      <c r="I53" s="8"/>
-      <c r="J53" s="8"/>
-      <c r="K53" s="8"/>
-      <c r="L53" s="8"/>
-      <c r="M53" s="8"/>
-      <c r="N53" s="8"/>
+      <c r="A53" s="11"/>
+      <c r="B53" s="12"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="12"/>
+      <c r="H53" s="12"/>
+      <c r="I53" s="12"/>
+      <c r="J53" s="12"/>
+      <c r="K53" s="12"/>
+      <c r="L53" s="12"/>
+      <c r="M53" s="12"/>
+      <c r="N53" s="12"/>
     </row>
     <row r="54" spans="1:14">
-      <c r="A54" s="7"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8"/>
-      <c r="G54" s="8"/>
-      <c r="H54" s="8"/>
-      <c r="I54" s="8"/>
-      <c r="J54" s="8"/>
-      <c r="K54" s="8"/>
-      <c r="L54" s="8"/>
-      <c r="M54" s="8"/>
-      <c r="N54" s="8"/>
+      <c r="A54" s="11"/>
+      <c r="B54" s="12"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="12"/>
+      <c r="I54" s="12"/>
+      <c r="J54" s="12"/>
+      <c r="K54" s="12"/>
+      <c r="L54" s="12"/>
+      <c r="M54" s="12"/>
+      <c r="N54" s="12"/>
     </row>
     <row r="55" spans="1:14">
-      <c r="A55" s="7"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="8"/>
-      <c r="G55" s="8"/>
-      <c r="H55" s="8"/>
-      <c r="I55" s="8"/>
-      <c r="J55" s="8"/>
-      <c r="K55" s="8"/>
-      <c r="L55" s="8"/>
-      <c r="M55" s="8"/>
-      <c r="N55" s="8"/>
+      <c r="A55" s="11"/>
+      <c r="B55" s="12"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="12"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="12"/>
+      <c r="H55" s="12"/>
+      <c r="I55" s="12"/>
+      <c r="J55" s="12"/>
+      <c r="K55" s="12"/>
+      <c r="L55" s="12"/>
+      <c r="M55" s="12"/>
+      <c r="N55" s="12"/>
     </row>
     <row r="56" spans="1:14">
-      <c r="A56" s="7"/>
-      <c r="B56" s="8"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8"/>
-      <c r="G56" s="8"/>
-      <c r="H56" s="8"/>
-      <c r="I56" s="8"/>
-      <c r="J56" s="8"/>
-      <c r="K56" s="8"/>
-      <c r="L56" s="8"/>
-      <c r="M56" s="8"/>
-      <c r="N56" s="8"/>
+      <c r="A56" s="11"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="12"/>
+      <c r="I56" s="12"/>
+      <c r="J56" s="12"/>
+      <c r="K56" s="12"/>
+      <c r="L56" s="12"/>
+      <c r="M56" s="12"/>
+      <c r="N56" s="12"/>
     </row>
     <row r="57" spans="1:14">
-      <c r="A57" s="7"/>
-      <c r="B57" s="8"/>
-      <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="8"/>
-      <c r="G57" s="8"/>
-      <c r="H57" s="8"/>
-      <c r="I57" s="8"/>
-      <c r="J57" s="8"/>
-      <c r="K57" s="8"/>
-      <c r="L57" s="8"/>
-      <c r="M57" s="8"/>
-      <c r="N57" s="8"/>
+      <c r="A57" s="11"/>
+      <c r="B57" s="12"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="12"/>
+      <c r="E57" s="12"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="12"/>
+      <c r="I57" s="12"/>
+      <c r="J57" s="12"/>
+      <c r="K57" s="12"/>
+      <c r="L57" s="12"/>
+      <c r="M57" s="12"/>
+      <c r="N57" s="12"/>
     </row>
     <row r="58" spans="1:14">
-      <c r="A58" s="7"/>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
-      <c r="G58" s="8"/>
-      <c r="H58" s="8"/>
-      <c r="I58" s="8"/>
-      <c r="J58" s="8"/>
-      <c r="K58" s="8"/>
-      <c r="L58" s="8"/>
-      <c r="M58" s="8"/>
-      <c r="N58" s="8"/>
+      <c r="A58" s="11"/>
+      <c r="B58" s="12"/>
+      <c r="C58" s="12"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="12"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="12"/>
+      <c r="H58" s="12"/>
+      <c r="I58" s="12"/>
+      <c r="J58" s="12"/>
+      <c r="K58" s="12"/>
+      <c r="L58" s="12"/>
+      <c r="M58" s="12"/>
+      <c r="N58" s="12"/>
     </row>
     <row r="59" spans="1:14">
-      <c r="A59" s="7"/>
-      <c r="B59" s="8"/>
-      <c r="C59" s="8"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8"/>
-      <c r="G59" s="8"/>
-      <c r="H59" s="8"/>
-      <c r="I59" s="8"/>
-      <c r="J59" s="8"/>
-      <c r="K59" s="8"/>
-      <c r="L59" s="8"/>
-      <c r="M59" s="8"/>
-      <c r="N59" s="8"/>
+      <c r="A59" s="11"/>
+      <c r="B59" s="12"/>
+      <c r="C59" s="12"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="12"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="12"/>
+      <c r="H59" s="12"/>
+      <c r="I59" s="12"/>
+      <c r="J59" s="12"/>
+      <c r="K59" s="12"/>
+      <c r="L59" s="12"/>
+      <c r="M59" s="12"/>
+      <c r="N59" s="12"/>
     </row>
     <row r="60" spans="1:14">
-      <c r="A60" s="7"/>
-      <c r="B60" s="8"/>
-      <c r="C60" s="8"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="8"/>
-      <c r="G60" s="8"/>
-      <c r="H60" s="8"/>
-      <c r="I60" s="8"/>
-      <c r="J60" s="8"/>
-      <c r="K60" s="8"/>
-      <c r="L60" s="8"/>
-      <c r="M60" s="8"/>
-      <c r="N60" s="8"/>
+      <c r="A60" s="11"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="12"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="12"/>
+      <c r="H60" s="12"/>
+      <c r="I60" s="12"/>
+      <c r="J60" s="12"/>
+      <c r="K60" s="12"/>
+      <c r="L60" s="12"/>
+      <c r="M60" s="12"/>
+      <c r="N60" s="12"/>
     </row>
     <row r="61" spans="1:14">
-      <c r="A61" s="7"/>
-      <c r="B61" s="8"/>
-      <c r="C61" s="8"/>
-      <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="8"/>
-      <c r="G61" s="8"/>
-      <c r="H61" s="8"/>
-      <c r="I61" s="8"/>
-      <c r="J61" s="8"/>
-      <c r="K61" s="8"/>
-      <c r="L61" s="8"/>
-      <c r="M61" s="8"/>
-      <c r="N61" s="8"/>
+      <c r="A61" s="11"/>
+      <c r="B61" s="12"/>
+      <c r="C61" s="12"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="12"/>
+      <c r="I61" s="12"/>
+      <c r="J61" s="12"/>
+      <c r="K61" s="12"/>
+      <c r="L61" s="12"/>
+      <c r="M61" s="12"/>
+      <c r="N61" s="12"/>
     </row>
     <row r="62" spans="1:14">
-      <c r="A62" s="7"/>
-      <c r="B62" s="8"/>
-      <c r="C62" s="8"/>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="8"/>
-      <c r="G62" s="8"/>
-      <c r="H62" s="8"/>
-      <c r="I62" s="8"/>
-      <c r="J62" s="8"/>
-      <c r="K62" s="8"/>
-      <c r="L62" s="8"/>
-      <c r="M62" s="8"/>
-      <c r="N62" s="8"/>
+      <c r="A62" s="11"/>
+      <c r="B62" s="12"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="12"/>
+      <c r="I62" s="12"/>
+      <c r="J62" s="12"/>
+      <c r="K62" s="12"/>
+      <c r="L62" s="12"/>
+      <c r="M62" s="12"/>
+      <c r="N62" s="12"/>
     </row>
     <row r="63" spans="1:14">
-      <c r="A63" s="7"/>
-      <c r="B63" s="8"/>
-      <c r="C63" s="8"/>
-      <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
-      <c r="F63" s="8"/>
-      <c r="G63" s="8"/>
-      <c r="H63" s="8"/>
-      <c r="I63" s="8"/>
-      <c r="J63" s="8"/>
-      <c r="K63" s="8"/>
-      <c r="L63" s="8"/>
-      <c r="M63" s="8"/>
-      <c r="N63" s="8"/>
+      <c r="A63" s="11"/>
+      <c r="B63" s="12"/>
+      <c r="C63" s="12"/>
+      <c r="D63" s="12"/>
+      <c r="E63" s="12"/>
+      <c r="F63" s="12"/>
+      <c r="G63" s="12"/>
+      <c r="H63" s="12"/>
+      <c r="I63" s="12"/>
+      <c r="J63" s="12"/>
+      <c r="K63" s="12"/>
+      <c r="L63" s="12"/>
+      <c r="M63" s="12"/>
+      <c r="N63" s="12"/>
     </row>
     <row r="64" spans="1:14">
-      <c r="A64" s="7"/>
-      <c r="B64" s="8"/>
-      <c r="C64" s="8"/>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="8"/>
-      <c r="G64" s="8"/>
-      <c r="H64" s="8"/>
-      <c r="I64" s="8"/>
-      <c r="J64" s="8"/>
-      <c r="K64" s="8"/>
-      <c r="L64" s="8"/>
-      <c r="M64" s="8"/>
-      <c r="N64" s="8"/>
+      <c r="A64" s="11"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="12"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="12"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12"/>
+      <c r="H64" s="12"/>
+      <c r="I64" s="12"/>
+      <c r="J64" s="12"/>
+      <c r="K64" s="12"/>
+      <c r="L64" s="12"/>
+      <c r="M64" s="12"/>
+      <c r="N64" s="12"/>
     </row>
     <row r="65" spans="1:14">
-      <c r="A65" s="7"/>
-      <c r="B65" s="8"/>
-      <c r="C65" s="8"/>
-      <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
-      <c r="F65" s="8"/>
-      <c r="G65" s="8"/>
-      <c r="H65" s="8"/>
-      <c r="I65" s="8"/>
-      <c r="J65" s="8"/>
-      <c r="K65" s="8"/>
-      <c r="L65" s="8"/>
-      <c r="M65" s="8"/>
-      <c r="N65" s="8"/>
+      <c r="A65" s="11"/>
+      <c r="B65" s="12"/>
+      <c r="C65" s="12"/>
+      <c r="D65" s="12"/>
+      <c r="E65" s="12"/>
+      <c r="F65" s="12"/>
+      <c r="G65" s="12"/>
+      <c r="H65" s="12"/>
+      <c r="I65" s="12"/>
+      <c r="J65" s="12"/>
+      <c r="K65" s="12"/>
+      <c r="L65" s="12"/>
+      <c r="M65" s="12"/>
+      <c r="N65" s="12"/>
     </row>
     <row r="66" spans="1:14">
-      <c r="A66" s="7"/>
-      <c r="B66" s="8"/>
-      <c r="C66" s="8"/>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="8"/>
-      <c r="G66" s="8"/>
-      <c r="H66" s="8"/>
-      <c r="I66" s="8"/>
-      <c r="J66" s="8"/>
-      <c r="K66" s="8"/>
-      <c r="L66" s="8"/>
-      <c r="M66" s="8"/>
-      <c r="N66" s="8"/>
+      <c r="A66" s="11"/>
+      <c r="B66" s="12"/>
+      <c r="C66" s="12"/>
+      <c r="D66" s="12"/>
+      <c r="E66" s="12"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12"/>
+      <c r="H66" s="12"/>
+      <c r="I66" s="12"/>
+      <c r="J66" s="12"/>
+      <c r="K66" s="12"/>
+      <c r="L66" s="12"/>
+      <c r="M66" s="12"/>
+      <c r="N66" s="12"/>
     </row>
     <row r="67" spans="1:14">
-      <c r="A67" s="7"/>
-      <c r="B67" s="8"/>
-      <c r="C67" s="8"/>
-      <c r="D67" s="8"/>
-      <c r="E67" s="8"/>
-      <c r="F67" s="8"/>
-      <c r="G67" s="8"/>
-      <c r="H67" s="8"/>
-      <c r="I67" s="8"/>
-      <c r="J67" s="8"/>
-      <c r="K67" s="8"/>
-      <c r="L67" s="8"/>
-      <c r="M67" s="8"/>
-      <c r="N67" s="8"/>
+      <c r="A67" s="11"/>
+      <c r="B67" s="12"/>
+      <c r="C67" s="12"/>
+      <c r="D67" s="12"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="12"/>
+      <c r="G67" s="12"/>
+      <c r="H67" s="12"/>
+      <c r="I67" s="12"/>
+      <c r="J67" s="12"/>
+      <c r="K67" s="12"/>
+      <c r="L67" s="12"/>
+      <c r="M67" s="12"/>
+      <c r="N67" s="12"/>
     </row>
     <row r="68" spans="1:14">
-      <c r="A68" s="7"/>
-      <c r="B68" s="8"/>
-      <c r="C68" s="8"/>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="8"/>
-      <c r="G68" s="8"/>
-      <c r="H68" s="8"/>
-      <c r="I68" s="8"/>
-      <c r="J68" s="8"/>
-      <c r="K68" s="8"/>
-      <c r="L68" s="8"/>
-      <c r="M68" s="8"/>
-      <c r="N68" s="8"/>
+      <c r="A68" s="11"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="12"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="12"/>
+      <c r="H68" s="12"/>
+      <c r="I68" s="12"/>
+      <c r="J68" s="12"/>
+      <c r="K68" s="12"/>
+      <c r="L68" s="12"/>
+      <c r="M68" s="12"/>
+      <c r="N68" s="12"/>
     </row>
     <row r="69" spans="1:14">
-      <c r="A69" s="7"/>
-      <c r="B69" s="8"/>
-      <c r="C69" s="8"/>
-      <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
-      <c r="F69" s="8"/>
-      <c r="G69" s="8"/>
-      <c r="H69" s="8"/>
-      <c r="I69" s="8"/>
-      <c r="J69" s="8"/>
-      <c r="K69" s="8"/>
-      <c r="L69" s="8"/>
-      <c r="M69" s="8"/>
-      <c r="N69" s="8"/>
+      <c r="A69" s="11"/>
+      <c r="B69" s="12"/>
+      <c r="C69" s="12"/>
+      <c r="D69" s="12"/>
+      <c r="E69" s="12"/>
+      <c r="F69" s="12"/>
+      <c r="G69" s="12"/>
+      <c r="H69" s="12"/>
+      <c r="I69" s="12"/>
+      <c r="J69" s="12"/>
+      <c r="K69" s="12"/>
+      <c r="L69" s="12"/>
+      <c r="M69" s="12"/>
+      <c r="N69" s="12"/>
     </row>
     <row r="70" spans="1:14">
-      <c r="A70" s="7"/>
-      <c r="B70" s="8"/>
-      <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="8"/>
-      <c r="G70" s="8"/>
-      <c r="H70" s="8"/>
-      <c r="I70" s="8"/>
-      <c r="J70" s="8"/>
-      <c r="K70" s="8"/>
-      <c r="L70" s="8"/>
-      <c r="M70" s="8"/>
-      <c r="N70" s="8"/>
+      <c r="A70" s="11"/>
+      <c r="B70" s="12"/>
+      <c r="C70" s="12"/>
+      <c r="D70" s="12"/>
+      <c r="E70" s="12"/>
+      <c r="F70" s="12"/>
+      <c r="G70" s="12"/>
+      <c r="H70" s="12"/>
+      <c r="I70" s="12"/>
+      <c r="J70" s="12"/>
+      <c r="K70" s="12"/>
+      <c r="L70" s="12"/>
+      <c r="M70" s="12"/>
+      <c r="N70" s="12"/>
     </row>
     <row r="71" spans="1:14">
-      <c r="A71" s="7"/>
-      <c r="B71" s="8"/>
-      <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
-      <c r="G71" s="8"/>
-      <c r="H71" s="8"/>
-      <c r="I71" s="8"/>
-      <c r="J71" s="8"/>
-      <c r="K71" s="8"/>
-      <c r="L71" s="8"/>
-      <c r="M71" s="8"/>
-      <c r="N71" s="8"/>
+      <c r="A71" s="11"/>
+      <c r="B71" s="12"/>
+      <c r="C71" s="12"/>
+      <c r="D71" s="12"/>
+      <c r="E71" s="12"/>
+      <c r="F71" s="12"/>
+      <c r="G71" s="12"/>
+      <c r="H71" s="12"/>
+      <c r="I71" s="12"/>
+      <c r="J71" s="12"/>
+      <c r="K71" s="12"/>
+      <c r="L71" s="12"/>
+      <c r="M71" s="12"/>
+      <c r="N71" s="12"/>
     </row>
     <row r="72" spans="1:14">
-      <c r="A72" s="7"/>
-      <c r="B72" s="8"/>
-      <c r="C72" s="8"/>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="8"/>
-      <c r="G72" s="8"/>
-      <c r="H72" s="8"/>
-      <c r="I72" s="8"/>
-      <c r="J72" s="8"/>
-      <c r="K72" s="8"/>
-      <c r="L72" s="8"/>
-      <c r="M72" s="8"/>
-      <c r="N72" s="8"/>
+      <c r="A72" s="11"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="12"/>
+      <c r="D72" s="12"/>
+      <c r="E72" s="12"/>
+      <c r="F72" s="12"/>
+      <c r="G72" s="12"/>
+      <c r="H72" s="12"/>
+      <c r="I72" s="12"/>
+      <c r="J72" s="12"/>
+      <c r="K72" s="12"/>
+      <c r="L72" s="12"/>
+      <c r="M72" s="12"/>
+      <c r="N72" s="12"/>
     </row>
     <row r="73" spans="1:14">
-      <c r="A73" s="7"/>
-      <c r="B73" s="8"/>
-      <c r="C73" s="8"/>
-      <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
-      <c r="F73" s="8"/>
-      <c r="G73" s="8"/>
-      <c r="H73" s="8"/>
-      <c r="I73" s="8"/>
-      <c r="J73" s="8"/>
-      <c r="K73" s="8"/>
-      <c r="L73" s="8"/>
-      <c r="M73" s="8"/>
-      <c r="N73" s="8"/>
+      <c r="A73" s="11"/>
+      <c r="B73" s="12"/>
+      <c r="C73" s="12"/>
+      <c r="D73" s="12"/>
+      <c r="E73" s="12"/>
+      <c r="F73" s="12"/>
+      <c r="G73" s="12"/>
+      <c r="H73" s="12"/>
+      <c r="I73" s="12"/>
+      <c r="J73" s="12"/>
+      <c r="K73" s="12"/>
+      <c r="L73" s="12"/>
+      <c r="M73" s="12"/>
+      <c r="N73" s="12"/>
     </row>
     <row r="74" spans="1:14">
-      <c r="A74" s="7"/>
-      <c r="B74" s="8"/>
-      <c r="C74" s="8"/>
-      <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="8"/>
-      <c r="G74" s="8"/>
-      <c r="H74" s="8"/>
-      <c r="I74" s="8"/>
-      <c r="J74" s="8"/>
-      <c r="K74" s="8"/>
-      <c r="L74" s="8"/>
-      <c r="M74" s="8"/>
-      <c r="N74" s="8"/>
+      <c r="A74" s="11"/>
+      <c r="B74" s="12"/>
+      <c r="C74" s="12"/>
+      <c r="D74" s="12"/>
+      <c r="E74" s="12"/>
+      <c r="F74" s="12"/>
+      <c r="G74" s="12"/>
+      <c r="H74" s="12"/>
+      <c r="I74" s="12"/>
+      <c r="J74" s="12"/>
+      <c r="K74" s="12"/>
+      <c r="L74" s="12"/>
+      <c r="M74" s="12"/>
+      <c r="N74" s="12"/>
     </row>
     <row r="75" spans="1:14">
-      <c r="A75" s="7"/>
-      <c r="B75" s="8"/>
-      <c r="C75" s="8"/>
-      <c r="D75" s="8"/>
-      <c r="E75" s="8"/>
-      <c r="F75" s="8"/>
-      <c r="G75" s="8"/>
-      <c r="H75" s="8"/>
-      <c r="I75" s="8"/>
-      <c r="J75" s="8"/>
-      <c r="K75" s="8"/>
-      <c r="L75" s="8"/>
-      <c r="M75" s="8"/>
-      <c r="N75" s="8"/>
+      <c r="A75" s="11"/>
+      <c r="B75" s="12"/>
+      <c r="C75" s="12"/>
+      <c r="D75" s="12"/>
+      <c r="E75" s="12"/>
+      <c r="F75" s="12"/>
+      <c r="G75" s="12"/>
+      <c r="H75" s="12"/>
+      <c r="I75" s="12"/>
+      <c r="J75" s="12"/>
+      <c r="K75" s="12"/>
+      <c r="L75" s="12"/>
+      <c r="M75" s="12"/>
+      <c r="N75" s="12"/>
     </row>
     <row r="76" spans="1:14">
-      <c r="A76" s="7"/>
-      <c r="B76" s="8"/>
-      <c r="C76" s="8"/>
-      <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="8"/>
-      <c r="G76" s="8"/>
-      <c r="H76" s="8"/>
-      <c r="I76" s="8"/>
-      <c r="J76" s="8"/>
-      <c r="K76" s="8"/>
-      <c r="L76" s="8"/>
-      <c r="M76" s="8"/>
-      <c r="N76" s="8"/>
+      <c r="A76" s="11"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="12"/>
+      <c r="D76" s="12"/>
+      <c r="E76" s="12"/>
+      <c r="F76" s="12"/>
+      <c r="G76" s="12"/>
+      <c r="H76" s="12"/>
+      <c r="I76" s="12"/>
+      <c r="J76" s="12"/>
+      <c r="K76" s="12"/>
+      <c r="L76" s="12"/>
+      <c r="M76" s="12"/>
+      <c r="N76" s="12"/>
     </row>
     <row r="77" spans="1:14">
-      <c r="A77" s="7"/>
-      <c r="B77" s="8"/>
-      <c r="C77" s="8"/>
-      <c r="D77" s="8"/>
-      <c r="E77" s="8"/>
-      <c r="F77" s="8"/>
-      <c r="G77" s="8"/>
-      <c r="H77" s="8"/>
-      <c r="I77" s="8"/>
-      <c r="J77" s="8"/>
-      <c r="K77" s="8"/>
-      <c r="L77" s="8"/>
-      <c r="M77" s="8"/>
-      <c r="N77" s="8"/>
+      <c r="A77" s="11"/>
+      <c r="B77" s="12"/>
+      <c r="C77" s="12"/>
+      <c r="D77" s="12"/>
+      <c r="E77" s="12"/>
+      <c r="F77" s="12"/>
+      <c r="G77" s="12"/>
+      <c r="H77" s="12"/>
+      <c r="I77" s="12"/>
+      <c r="J77" s="12"/>
+      <c r="K77" s="12"/>
+      <c r="L77" s="12"/>
+      <c r="M77" s="12"/>
+      <c r="N77" s="12"/>
     </row>
     <row r="78" spans="1:14">
-      <c r="A78" s="7"/>
-      <c r="B78" s="8"/>
-      <c r="C78" s="8"/>
-      <c r="D78" s="8"/>
-      <c r="E78" s="8"/>
-      <c r="F78" s="8"/>
-      <c r="G78" s="8"/>
-      <c r="H78" s="8"/>
-      <c r="I78" s="8"/>
-      <c r="J78" s="8"/>
-      <c r="K78" s="8"/>
-      <c r="L78" s="8"/>
-      <c r="M78" s="8"/>
-      <c r="N78" s="8"/>
+      <c r="A78" s="11"/>
+      <c r="B78" s="12"/>
+      <c r="C78" s="12"/>
+      <c r="D78" s="12"/>
+      <c r="E78" s="12"/>
+      <c r="F78" s="12"/>
+      <c r="G78" s="12"/>
+      <c r="H78" s="12"/>
+      <c r="I78" s="12"/>
+      <c r="J78" s="12"/>
+      <c r="K78" s="12"/>
+      <c r="L78" s="12"/>
+      <c r="M78" s="12"/>
+      <c r="N78" s="12"/>
     </row>
     <row r="79" spans="1:14">
-      <c r="A79" s="7"/>
-      <c r="B79" s="8"/>
-      <c r="C79" s="8"/>
-      <c r="D79" s="8"/>
-      <c r="E79" s="8"/>
-      <c r="F79" s="8"/>
-      <c r="G79" s="8"/>
-      <c r="H79" s="8"/>
-      <c r="I79" s="8"/>
-      <c r="J79" s="8"/>
-      <c r="K79" s="8"/>
-      <c r="L79" s="8"/>
-      <c r="M79" s="8"/>
-      <c r="N79" s="8"/>
+      <c r="A79" s="11"/>
+      <c r="B79" s="12"/>
+      <c r="C79" s="12"/>
+      <c r="D79" s="12"/>
+      <c r="E79" s="12"/>
+      <c r="F79" s="12"/>
+      <c r="G79" s="12"/>
+      <c r="H79" s="12"/>
+      <c r="I79" s="12"/>
+      <c r="J79" s="12"/>
+      <c r="K79" s="12"/>
+      <c r="L79" s="12"/>
+      <c r="M79" s="12"/>
+      <c r="N79" s="12"/>
     </row>
     <row r="80" spans="1:14">
-      <c r="A80" s="7"/>
-      <c r="B80" s="8"/>
-      <c r="C80" s="8"/>
-      <c r="D80" s="8"/>
-      <c r="E80" s="8"/>
-      <c r="F80" s="8"/>
-      <c r="G80" s="8"/>
-      <c r="H80" s="8"/>
-      <c r="I80" s="8"/>
-      <c r="J80" s="8"/>
-      <c r="K80" s="8"/>
-      <c r="L80" s="8"/>
-      <c r="M80" s="8"/>
-      <c r="N80" s="8"/>
+      <c r="A80" s="11"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="12"/>
+      <c r="D80" s="12"/>
+      <c r="E80" s="12"/>
+      <c r="F80" s="12"/>
+      <c r="G80" s="12"/>
+      <c r="H80" s="12"/>
+      <c r="I80" s="12"/>
+      <c r="J80" s="12"/>
+      <c r="K80" s="12"/>
+      <c r="L80" s="12"/>
+      <c r="M80" s="12"/>
+      <c r="N80" s="12"/>
     </row>
     <row r="81" spans="1:14">
-      <c r="A81" s="7"/>
-      <c r="B81" s="8"/>
-      <c r="C81" s="8"/>
-      <c r="D81" s="8"/>
-      <c r="E81" s="8"/>
-      <c r="F81" s="8"/>
-      <c r="G81" s="8"/>
-      <c r="H81" s="8"/>
-      <c r="I81" s="8"/>
-      <c r="J81" s="8"/>
-      <c r="K81" s="8"/>
-      <c r="L81" s="8"/>
-      <c r="M81" s="8"/>
-      <c r="N81" s="8"/>
+      <c r="A81" s="11"/>
+      <c r="B81" s="12"/>
+      <c r="C81" s="12"/>
+      <c r="D81" s="12"/>
+      <c r="E81" s="12"/>
+      <c r="F81" s="12"/>
+      <c r="G81" s="12"/>
+      <c r="H81" s="12"/>
+      <c r="I81" s="12"/>
+      <c r="J81" s="12"/>
+      <c r="K81" s="12"/>
+      <c r="L81" s="12"/>
+      <c r="M81" s="12"/>
+      <c r="N81" s="12"/>
     </row>
     <row r="82" spans="1:14">
-      <c r="A82" s="7"/>
-      <c r="B82" s="8"/>
-      <c r="C82" s="8"/>
-      <c r="D82" s="8"/>
-      <c r="E82" s="8"/>
-      <c r="F82" s="8"/>
-      <c r="G82" s="8"/>
-      <c r="H82" s="8"/>
-      <c r="I82" s="8"/>
-      <c r="J82" s="8"/>
-      <c r="K82" s="8"/>
-      <c r="L82" s="8"/>
-      <c r="M82" s="8"/>
-      <c r="N82" s="8"/>
+      <c r="A82" s="11"/>
+      <c r="B82" s="12"/>
+      <c r="C82" s="12"/>
+      <c r="D82" s="12"/>
+      <c r="E82" s="12"/>
+      <c r="F82" s="12"/>
+      <c r="G82" s="12"/>
+      <c r="H82" s="12"/>
+      <c r="I82" s="12"/>
+      <c r="J82" s="12"/>
+      <c r="K82" s="12"/>
+      <c r="L82" s="12"/>
+      <c r="M82" s="12"/>
+      <c r="N82" s="12"/>
     </row>
     <row r="83" spans="1:14">
-      <c r="A83" s="7"/>
-      <c r="B83" s="8"/>
-      <c r="C83" s="8"/>
-      <c r="D83" s="8"/>
-      <c r="E83" s="8"/>
-      <c r="F83" s="8"/>
-      <c r="G83" s="8"/>
-      <c r="H83" s="8"/>
-      <c r="I83" s="8"/>
-      <c r="J83" s="8"/>
-      <c r="K83" s="8"/>
-      <c r="L83" s="8"/>
-      <c r="M83" s="8"/>
-      <c r="N83" s="8"/>
+      <c r="A83" s="11"/>
+      <c r="B83" s="12"/>
+      <c r="C83" s="12"/>
+      <c r="D83" s="12"/>
+      <c r="E83" s="12"/>
+      <c r="F83" s="12"/>
+      <c r="G83" s="12"/>
+      <c r="H83" s="12"/>
+      <c r="I83" s="12"/>
+      <c r="J83" s="12"/>
+      <c r="K83" s="12"/>
+      <c r="L83" s="12"/>
+      <c r="M83" s="12"/>
+      <c r="N83" s="12"/>
     </row>
     <row r="84" spans="1:14">
-      <c r="A84" s="7"/>
-      <c r="B84" s="8"/>
-      <c r="C84" s="8"/>
-      <c r="D84" s="8"/>
-      <c r="E84" s="8"/>
-      <c r="F84" s="8"/>
-      <c r="G84" s="8"/>
-      <c r="H84" s="8"/>
-      <c r="I84" s="8"/>
-      <c r="J84" s="8"/>
-      <c r="K84" s="8"/>
-      <c r="L84" s="8"/>
-      <c r="M84" s="8"/>
-      <c r="N84" s="8"/>
+      <c r="A84" s="11"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="12"/>
+      <c r="D84" s="12"/>
+      <c r="E84" s="12"/>
+      <c r="F84" s="12"/>
+      <c r="G84" s="12"/>
+      <c r="H84" s="12"/>
+      <c r="I84" s="12"/>
+      <c r="J84" s="12"/>
+      <c r="K84" s="12"/>
+      <c r="L84" s="12"/>
+      <c r="M84" s="12"/>
+      <c r="N84" s="12"/>
     </row>
     <row r="85" spans="1:14">
-      <c r="A85" s="7"/>
-      <c r="B85" s="8"/>
-      <c r="C85" s="8"/>
-      <c r="D85" s="8"/>
-      <c r="E85" s="8"/>
-      <c r="F85" s="8"/>
-      <c r="G85" s="8"/>
-      <c r="H85" s="8"/>
-      <c r="I85" s="8"/>
-      <c r="J85" s="8"/>
-      <c r="K85" s="8"/>
-      <c r="L85" s="8"/>
-      <c r="M85" s="8"/>
-      <c r="N85" s="8"/>
+      <c r="A85" s="11"/>
+      <c r="B85" s="12"/>
+      <c r="C85" s="12"/>
+      <c r="D85" s="12"/>
+      <c r="E85" s="12"/>
+      <c r="F85" s="12"/>
+      <c r="G85" s="12"/>
+      <c r="H85" s="12"/>
+      <c r="I85" s="12"/>
+      <c r="J85" s="12"/>
+      <c r="K85" s="12"/>
+      <c r="L85" s="12"/>
+      <c r="M85" s="12"/>
+      <c r="N85" s="12"/>
     </row>
     <row r="86" spans="1:14">
-      <c r="A86" s="7"/>
-      <c r="B86" s="8"/>
-      <c r="C86" s="8"/>
-      <c r="D86" s="8"/>
-      <c r="E86" s="8"/>
-      <c r="F86" s="8"/>
-      <c r="G86" s="8"/>
-      <c r="H86" s="8"/>
-      <c r="I86" s="8"/>
-      <c r="J86" s="8"/>
-      <c r="K86" s="8"/>
-      <c r="L86" s="8"/>
-      <c r="M86" s="8"/>
-      <c r="N86" s="8"/>
+      <c r="A86" s="11"/>
+      <c r="B86" s="12"/>
+      <c r="C86" s="12"/>
+      <c r="D86" s="12"/>
+      <c r="E86" s="12"/>
+      <c r="F86" s="12"/>
+      <c r="G86" s="12"/>
+      <c r="H86" s="12"/>
+      <c r="I86" s="12"/>
+      <c r="J86" s="12"/>
+      <c r="K86" s="12"/>
+      <c r="L86" s="12"/>
+      <c r="M86" s="12"/>
+      <c r="N86" s="12"/>
     </row>
     <row r="87" spans="1:14">
-      <c r="A87" s="7"/>
-      <c r="B87" s="8"/>
-      <c r="C87" s="8"/>
-      <c r="D87" s="8"/>
-      <c r="E87" s="8"/>
-      <c r="F87" s="8"/>
-      <c r="G87" s="8"/>
-      <c r="H87" s="8"/>
-      <c r="I87" s="8"/>
-      <c r="J87" s="8"/>
-      <c r="K87" s="8"/>
-      <c r="L87" s="8"/>
-      <c r="M87" s="8"/>
-      <c r="N87" s="8"/>
+      <c r="A87" s="11"/>
+      <c r="B87" s="12"/>
+      <c r="C87" s="12"/>
+      <c r="D87" s="12"/>
+      <c r="E87" s="12"/>
+      <c r="F87" s="12"/>
+      <c r="G87" s="12"/>
+      <c r="H87" s="12"/>
+      <c r="I87" s="12"/>
+      <c r="J87" s="12"/>
+      <c r="K87" s="12"/>
+      <c r="L87" s="12"/>
+      <c r="M87" s="12"/>
+      <c r="N87" s="12"/>
     </row>
     <row r="88" spans="1:14">
-      <c r="A88" s="7"/>
-      <c r="B88" s="8"/>
-      <c r="C88" s="8"/>
-      <c r="D88" s="8"/>
-      <c r="E88" s="8"/>
-      <c r="F88" s="8"/>
-      <c r="G88" s="8"/>
-      <c r="H88" s="8"/>
-      <c r="I88" s="8"/>
-      <c r="J88" s="8"/>
-      <c r="K88" s="8"/>
-      <c r="L88" s="8"/>
-      <c r="M88" s="8"/>
-      <c r="N88" s="8"/>
+      <c r="A88" s="11"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="12"/>
+      <c r="D88" s="12"/>
+      <c r="E88" s="12"/>
+      <c r="F88" s="12"/>
+      <c r="G88" s="12"/>
+      <c r="H88" s="12"/>
+      <c r="I88" s="12"/>
+      <c r="J88" s="12"/>
+      <c r="K88" s="12"/>
+      <c r="L88" s="12"/>
+      <c r="M88" s="12"/>
+      <c r="N88" s="12"/>
     </row>
     <row r="89" spans="1:14">
-      <c r="A89" s="7"/>
-      <c r="B89" s="8"/>
-      <c r="C89" s="8"/>
-      <c r="D89" s="8"/>
-      <c r="E89" s="8"/>
-      <c r="F89" s="8"/>
-      <c r="G89" s="8"/>
-      <c r="H89" s="8"/>
-      <c r="I89" s="8"/>
-      <c r="J89" s="8"/>
-      <c r="K89" s="8"/>
-      <c r="L89" s="8"/>
-      <c r="M89" s="8"/>
-      <c r="N89" s="8"/>
+      <c r="A89" s="11"/>
+      <c r="B89" s="12"/>
+      <c r="C89" s="12"/>
+      <c r="D89" s="12"/>
+      <c r="E89" s="12"/>
+      <c r="F89" s="12"/>
+      <c r="G89" s="12"/>
+      <c r="H89" s="12"/>
+      <c r="I89" s="12"/>
+      <c r="J89" s="12"/>
+      <c r="K89" s="12"/>
+      <c r="L89" s="12"/>
+      <c r="M89" s="12"/>
+      <c r="N89" s="12"/>
     </row>
     <row r="90" spans="1:14">
-      <c r="A90" s="7"/>
-      <c r="B90" s="8"/>
-      <c r="C90" s="8"/>
-      <c r="D90" s="8"/>
-      <c r="E90" s="8"/>
-      <c r="F90" s="8"/>
-      <c r="G90" s="8"/>
-      <c r="H90" s="8"/>
-      <c r="I90" s="8"/>
-      <c r="J90" s="8"/>
-      <c r="K90" s="8"/>
-      <c r="L90" s="8"/>
-      <c r="M90" s="8"/>
-      <c r="N90" s="8"/>
+      <c r="A90" s="11"/>
+      <c r="B90" s="12"/>
+      <c r="C90" s="12"/>
+      <c r="D90" s="12"/>
+      <c r="E90" s="12"/>
+      <c r="F90" s="12"/>
+      <c r="G90" s="12"/>
+      <c r="H90" s="12"/>
+      <c r="I90" s="12"/>
+      <c r="J90" s="12"/>
+      <c r="K90" s="12"/>
+      <c r="L90" s="12"/>
+      <c r="M90" s="12"/>
+      <c r="N90" s="12"/>
     </row>
     <row r="91" spans="1:14">
-      <c r="A91" s="7"/>
-      <c r="B91" s="8"/>
-      <c r="C91" s="8"/>
-      <c r="D91" s="8"/>
-      <c r="E91" s="8"/>
-      <c r="F91" s="8"/>
-      <c r="G91" s="8"/>
-      <c r="H91" s="8"/>
-      <c r="I91" s="8"/>
-      <c r="J91" s="8"/>
-      <c r="K91" s="8"/>
-      <c r="L91" s="8"/>
-      <c r="M91" s="8"/>
-      <c r="N91" s="8"/>
+      <c r="A91" s="11"/>
+      <c r="B91" s="12"/>
+      <c r="C91" s="12"/>
+      <c r="D91" s="12"/>
+      <c r="E91" s="12"/>
+      <c r="F91" s="12"/>
+      <c r="G91" s="12"/>
+      <c r="H91" s="12"/>
+      <c r="I91" s="12"/>
+      <c r="J91" s="12"/>
+      <c r="K91" s="12"/>
+      <c r="L91" s="12"/>
+      <c r="M91" s="12"/>
+      <c r="N91" s="12"/>
     </row>
     <row r="92" spans="1:14">
-      <c r="A92" s="7"/>
-      <c r="B92" s="8"/>
-      <c r="C92" s="8"/>
-      <c r="D92" s="8"/>
-      <c r="E92" s="8"/>
-      <c r="F92" s="8"/>
-      <c r="G92" s="8"/>
-      <c r="H92" s="8"/>
-      <c r="I92" s="8"/>
-      <c r="J92" s="8"/>
-      <c r="K92" s="8"/>
-      <c r="L92" s="8"/>
-      <c r="M92" s="8"/>
-      <c r="N92" s="8"/>
+      <c r="A92" s="11"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="12"/>
+      <c r="D92" s="12"/>
+      <c r="E92" s="12"/>
+      <c r="F92" s="12"/>
+      <c r="G92" s="12"/>
+      <c r="H92" s="12"/>
+      <c r="I92" s="12"/>
+      <c r="J92" s="12"/>
+      <c r="K92" s="12"/>
+      <c r="L92" s="12"/>
+      <c r="M92" s="12"/>
+      <c r="N92" s="12"/>
     </row>
     <row r="93" spans="1:14">
-      <c r="A93" s="7"/>
-      <c r="B93" s="8"/>
-      <c r="C93" s="8"/>
-      <c r="D93" s="8"/>
-      <c r="E93" s="8"/>
-      <c r="F93" s="8"/>
-      <c r="G93" s="8"/>
-      <c r="H93" s="8"/>
-      <c r="I93" s="8"/>
-      <c r="J93" s="8"/>
-      <c r="K93" s="8"/>
-      <c r="L93" s="8"/>
-      <c r="M93" s="8"/>
-      <c r="N93" s="8"/>
+      <c r="A93" s="11"/>
+      <c r="B93" s="12"/>
+      <c r="C93" s="12"/>
+      <c r="D93" s="12"/>
+      <c r="E93" s="12"/>
+      <c r="F93" s="12"/>
+      <c r="G93" s="12"/>
+      <c r="H93" s="12"/>
+      <c r="I93" s="12"/>
+      <c r="J93" s="12"/>
+      <c r="K93" s="12"/>
+      <c r="L93" s="12"/>
+      <c r="M93" s="12"/>
+      <c r="N93" s="12"/>
     </row>
     <row r="94" spans="1:14">
-      <c r="A94" s="7"/>
-      <c r="B94" s="8"/>
-      <c r="C94" s="8"/>
-      <c r="D94" s="8"/>
-      <c r="E94" s="8"/>
-      <c r="F94" s="8"/>
-      <c r="G94" s="8"/>
-      <c r="H94" s="8"/>
-      <c r="I94" s="8"/>
-      <c r="J94" s="8"/>
-      <c r="K94" s="8"/>
-      <c r="L94" s="8"/>
-      <c r="M94" s="8"/>
-      <c r="N94" s="8"/>
+      <c r="A94" s="11"/>
+      <c r="B94" s="12"/>
+      <c r="C94" s="12"/>
+      <c r="D94" s="12"/>
+      <c r="E94" s="12"/>
+      <c r="F94" s="12"/>
+      <c r="G94" s="12"/>
+      <c r="H94" s="12"/>
+      <c r="I94" s="12"/>
+      <c r="J94" s="12"/>
+      <c r="K94" s="12"/>
+      <c r="L94" s="12"/>
+      <c r="M94" s="12"/>
+      <c r="N94" s="12"/>
     </row>
     <row r="95" spans="1:14">
-      <c r="A95" s="7"/>
-      <c r="B95" s="8"/>
-      <c r="C95" s="8"/>
-      <c r="D95" s="8"/>
-      <c r="E95" s="8"/>
-      <c r="F95" s="8"/>
-      <c r="G95" s="8"/>
-      <c r="H95" s="8"/>
-      <c r="I95" s="8"/>
-      <c r="J95" s="8"/>
-      <c r="K95" s="8"/>
-      <c r="L95" s="8"/>
-      <c r="M95" s="8"/>
-      <c r="N95" s="8"/>
+      <c r="A95" s="11"/>
+      <c r="B95" s="12"/>
+      <c r="C95" s="12"/>
+      <c r="D95" s="12"/>
+      <c r="E95" s="12"/>
+      <c r="F95" s="12"/>
+      <c r="G95" s="12"/>
+      <c r="H95" s="12"/>
+      <c r="I95" s="12"/>
+      <c r="J95" s="12"/>
+      <c r="K95" s="12"/>
+      <c r="L95" s="12"/>
+      <c r="M95" s="12"/>
+      <c r="N95" s="12"/>
     </row>
     <row r="96" spans="1:14">
-      <c r="A96" s="7"/>
-      <c r="B96" s="8"/>
-      <c r="C96" s="8"/>
-      <c r="D96" s="8"/>
-      <c r="E96" s="8"/>
-      <c r="F96" s="8"/>
-      <c r="G96" s="8"/>
-      <c r="H96" s="8"/>
-      <c r="I96" s="8"/>
-      <c r="J96" s="8"/>
-      <c r="K96" s="8"/>
-      <c r="L96" s="8"/>
-      <c r="M96" s="8"/>
-      <c r="N96" s="8"/>
+      <c r="A96" s="11"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="12"/>
+      <c r="D96" s="12"/>
+      <c r="E96" s="12"/>
+      <c r="F96" s="12"/>
+      <c r="G96" s="12"/>
+      <c r="H96" s="12"/>
+      <c r="I96" s="12"/>
+      <c r="J96" s="12"/>
+      <c r="K96" s="12"/>
+      <c r="L96" s="12"/>
+      <c r="M96" s="12"/>
+      <c r="N96" s="12"/>
     </row>
     <row r="97" spans="1:14">
-      <c r="A97" s="7"/>
-      <c r="B97" s="8"/>
-      <c r="C97" s="8"/>
-      <c r="D97" s="8"/>
-      <c r="E97" s="8"/>
-      <c r="F97" s="8"/>
-      <c r="G97" s="8"/>
-      <c r="H97" s="8"/>
-      <c r="I97" s="8"/>
-      <c r="J97" s="8"/>
-      <c r="K97" s="8"/>
-      <c r="L97" s="8"/>
-      <c r="M97" s="8"/>
-      <c r="N97" s="8"/>
+      <c r="A97" s="11"/>
+      <c r="B97" s="12"/>
+      <c r="C97" s="12"/>
+      <c r="D97" s="12"/>
+      <c r="E97" s="12"/>
+      <c r="F97" s="12"/>
+      <c r="G97" s="12"/>
+      <c r="H97" s="12"/>
+      <c r="I97" s="12"/>
+      <c r="J97" s="12"/>
+      <c r="K97" s="12"/>
+      <c r="L97" s="12"/>
+      <c r="M97" s="12"/>
+      <c r="N97" s="12"/>
     </row>
     <row r="98" spans="1:14">
-      <c r="A98" s="7"/>
-      <c r="B98" s="8"/>
-      <c r="C98" s="8"/>
-      <c r="D98" s="8"/>
-      <c r="E98" s="8"/>
-      <c r="F98" s="8"/>
-      <c r="G98" s="8"/>
-      <c r="H98" s="8"/>
-      <c r="I98" s="8"/>
-      <c r="J98" s="8"/>
-      <c r="K98" s="8"/>
-      <c r="L98" s="8"/>
-      <c r="M98" s="8"/>
-      <c r="N98" s="8"/>
+      <c r="A98" s="11"/>
+      <c r="B98" s="12"/>
+      <c r="C98" s="12"/>
+      <c r="D98" s="12"/>
+      <c r="E98" s="12"/>
+      <c r="F98" s="12"/>
+      <c r="G98" s="12"/>
+      <c r="H98" s="12"/>
+      <c r="I98" s="12"/>
+      <c r="J98" s="12"/>
+      <c r="K98" s="12"/>
+      <c r="L98" s="12"/>
+      <c r="M98" s="12"/>
+      <c r="N98" s="12"/>
     </row>
     <row r="99" spans="1:14">
-      <c r="A99" s="7"/>
-      <c r="B99" s="8"/>
-      <c r="C99" s="8"/>
-      <c r="D99" s="8"/>
-      <c r="E99" s="8"/>
-      <c r="F99" s="8"/>
-      <c r="G99" s="8"/>
-      <c r="H99" s="8"/>
-      <c r="I99" s="8"/>
-      <c r="J99" s="8"/>
-      <c r="K99" s="8"/>
-      <c r="L99" s="8"/>
-      <c r="M99" s="8"/>
-      <c r="N99" s="8"/>
+      <c r="A99" s="11"/>
+      <c r="B99" s="12"/>
+      <c r="C99" s="12"/>
+      <c r="D99" s="12"/>
+      <c r="E99" s="12"/>
+      <c r="F99" s="12"/>
+      <c r="G99" s="12"/>
+      <c r="H99" s="12"/>
+      <c r="I99" s="12"/>
+      <c r="J99" s="12"/>
+      <c r="K99" s="12"/>
+      <c r="L99" s="12"/>
+      <c r="M99" s="12"/>
+      <c r="N99" s="12"/>
     </row>
     <row r="100" spans="1:14">
-      <c r="A100" s="7"/>
-      <c r="B100" s="8"/>
-      <c r="C100" s="8"/>
-      <c r="D100" s="8"/>
-      <c r="E100" s="8"/>
-      <c r="F100" s="8"/>
-      <c r="G100" s="8"/>
-      <c r="H100" s="8"/>
-      <c r="I100" s="8"/>
-      <c r="J100" s="8"/>
-      <c r="K100" s="8"/>
-      <c r="L100" s="8"/>
-      <c r="M100" s="8"/>
-      <c r="N100" s="8"/>
+      <c r="A100" s="11"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="12"/>
+      <c r="D100" s="12"/>
+      <c r="E100" s="12"/>
+      <c r="F100" s="12"/>
+      <c r="G100" s="12"/>
+      <c r="H100" s="12"/>
+      <c r="I100" s="12"/>
+      <c r="J100" s="12"/>
+      <c r="K100" s="12"/>
+      <c r="L100" s="12"/>
+      <c r="M100" s="12"/>
+      <c r="N100" s="12"/>
     </row>
     <row r="101" spans="1:14">
-      <c r="A101" s="7"/>
-      <c r="B101" s="8"/>
-      <c r="C101" s="8"/>
-      <c r="D101" s="8"/>
-      <c r="E101" s="8"/>
-      <c r="F101" s="8"/>
-      <c r="G101" s="8"/>
-      <c r="H101" s="8"/>
-      <c r="I101" s="8"/>
-      <c r="J101" s="8"/>
-      <c r="K101" s="8"/>
-      <c r="L101" s="8"/>
-      <c r="M101" s="8"/>
-      <c r="N101" s="8"/>
+      <c r="A101" s="11"/>
+      <c r="B101" s="12"/>
+      <c r="C101" s="12"/>
+      <c r="D101" s="12"/>
+      <c r="E101" s="12"/>
+      <c r="F101" s="12"/>
+      <c r="G101" s="12"/>
+      <c r="H101" s="12"/>
+      <c r="I101" s="12"/>
+      <c r="J101" s="12"/>
+      <c r="K101" s="12"/>
+      <c r="L101" s="12"/>
+      <c r="M101" s="12"/>
+      <c r="N101" s="12"/>
     </row>
     <row r="102" spans="1:14">
-      <c r="A102" s="7"/>
-      <c r="B102" s="8"/>
-      <c r="C102" s="8"/>
-      <c r="D102" s="8"/>
-      <c r="E102" s="8"/>
-      <c r="F102" s="8"/>
-      <c r="G102" s="8"/>
-      <c r="H102" s="8"/>
-      <c r="I102" s="8"/>
-      <c r="J102" s="8"/>
-      <c r="K102" s="8"/>
-      <c r="L102" s="8"/>
-      <c r="M102" s="8"/>
-      <c r="N102" s="8"/>
+      <c r="A102" s="11"/>
+      <c r="B102" s="12"/>
+      <c r="C102" s="12"/>
+      <c r="D102" s="12"/>
+      <c r="E102" s="12"/>
+      <c r="F102" s="12"/>
+      <c r="G102" s="12"/>
+      <c r="H102" s="12"/>
+      <c r="I102" s="12"/>
+      <c r="J102" s="12"/>
+      <c r="K102" s="12"/>
+      <c r="L102" s="12"/>
+      <c r="M102" s="12"/>
+      <c r="N102" s="12"/>
     </row>
     <row r="103" spans="1:14">
-      <c r="A103" s="7"/>
-      <c r="B103" s="8"/>
-      <c r="C103" s="8"/>
-      <c r="D103" s="8"/>
-      <c r="E103" s="8"/>
-      <c r="F103" s="8"/>
-      <c r="G103" s="8"/>
-      <c r="H103" s="8"/>
-      <c r="I103" s="8"/>
-      <c r="J103" s="8"/>
-      <c r="K103" s="8"/>
-      <c r="L103" s="8"/>
-      <c r="M103" s="8"/>
-      <c r="N103" s="8"/>
+      <c r="A103" s="11"/>
+      <c r="B103" s="12"/>
+      <c r="C103" s="12"/>
+      <c r="D103" s="12"/>
+      <c r="E103" s="12"/>
+      <c r="F103" s="12"/>
+      <c r="G103" s="12"/>
+      <c r="H103" s="12"/>
+      <c r="I103" s="12"/>
+      <c r="J103" s="12"/>
+      <c r="K103" s="12"/>
+      <c r="L103" s="12"/>
+      <c r="M103" s="12"/>
+      <c r="N103" s="12"/>
     </row>
     <row r="104" spans="1:14">
-      <c r="A104" s="7"/>
-      <c r="B104" s="8"/>
-      <c r="C104" s="8"/>
-      <c r="D104" s="8"/>
-      <c r="E104" s="8"/>
-      <c r="F104" s="8"/>
-      <c r="G104" s="8"/>
-      <c r="H104" s="8"/>
-      <c r="I104" s="8"/>
-      <c r="J104" s="8"/>
-      <c r="K104" s="8"/>
-      <c r="L104" s="8"/>
-      <c r="M104" s="8"/>
-      <c r="N104" s="8"/>
+      <c r="A104" s="11"/>
+      <c r="B104" s="12"/>
+      <c r="C104" s="12"/>
+      <c r="D104" s="12"/>
+      <c r="E104" s="12"/>
+      <c r="F104" s="12"/>
+      <c r="G104" s="12"/>
+      <c r="H104" s="12"/>
+      <c r="I104" s="12"/>
+      <c r="J104" s="12"/>
+      <c r="K104" s="12"/>
+      <c r="L104" s="12"/>
+      <c r="M104" s="12"/>
+      <c r="N104" s="12"/>
     </row>
     <row r="105" spans="1:14">
-      <c r="A105" s="7"/>
-      <c r="B105" s="8"/>
-      <c r="C105" s="8"/>
-      <c r="D105" s="8"/>
-      <c r="E105" s="8"/>
-      <c r="F105" s="8"/>
-      <c r="G105" s="8"/>
-      <c r="H105" s="8"/>
-      <c r="I105" s="8"/>
-      <c r="J105" s="8"/>
-      <c r="K105" s="8"/>
-      <c r="L105" s="8"/>
-      <c r="M105" s="8"/>
-      <c r="N105" s="8"/>
+      <c r="A105" s="11"/>
+      <c r="B105" s="12"/>
+      <c r="C105" s="12"/>
+      <c r="D105" s="12"/>
+      <c r="E105" s="12"/>
+      <c r="F105" s="12"/>
+      <c r="G105" s="12"/>
+      <c r="H105" s="12"/>
+      <c r="I105" s="12"/>
+      <c r="J105" s="12"/>
+      <c r="K105" s="12"/>
+      <c r="L105" s="12"/>
+      <c r="M105" s="12"/>
+      <c r="N105" s="12"/>
     </row>
     <row r="106" spans="1:14">
-      <c r="A106" s="7"/>
-      <c r="B106" s="8"/>
-      <c r="C106" s="8"/>
-      <c r="D106" s="8"/>
-      <c r="E106" s="8"/>
-      <c r="F106" s="8"/>
-      <c r="G106" s="8"/>
-      <c r="H106" s="8"/>
-      <c r="I106" s="8"/>
-      <c r="J106" s="8"/>
-      <c r="K106" s="8"/>
-      <c r="L106" s="8"/>
-      <c r="M106" s="8"/>
-      <c r="N106" s="8"/>
+      <c r="A106" s="11"/>
+      <c r="B106" s="12"/>
+      <c r="C106" s="12"/>
+      <c r="D106" s="12"/>
+      <c r="E106" s="12"/>
+      <c r="F106" s="12"/>
+      <c r="G106" s="12"/>
+      <c r="H106" s="12"/>
+      <c r="I106" s="12"/>
+      <c r="J106" s="12"/>
+      <c r="K106" s="12"/>
+      <c r="L106" s="12"/>
+      <c r="M106" s="12"/>
+      <c r="N106" s="12"/>
     </row>
     <row r="107" spans="1:14">
-      <c r="A107" s="7"/>
-      <c r="B107" s="8"/>
-      <c r="C107" s="8"/>
-      <c r="D107" s="8"/>
-      <c r="E107" s="8"/>
-      <c r="F107" s="8"/>
-      <c r="G107" s="8"/>
-      <c r="H107" s="8"/>
-      <c r="I107" s="8"/>
-      <c r="J107" s="8"/>
-      <c r="K107" s="8"/>
-      <c r="L107" s="8"/>
-      <c r="M107" s="8"/>
-      <c r="N107" s="8"/>
+      <c r="A107" s="11"/>
+      <c r="B107" s="12"/>
+      <c r="C107" s="12"/>
+      <c r="D107" s="12"/>
+      <c r="E107" s="12"/>
+      <c r="F107" s="12"/>
+      <c r="G107" s="12"/>
+      <c r="H107" s="12"/>
+      <c r="I107" s="12"/>
+      <c r="J107" s="12"/>
+      <c r="K107" s="12"/>
+      <c r="L107" s="12"/>
+      <c r="M107" s="12"/>
+      <c r="N107" s="12"/>
     </row>
     <row r="108" spans="1:14">
-      <c r="A108" s="7"/>
-      <c r="B108" s="8"/>
-      <c r="C108" s="8"/>
-      <c r="D108" s="8"/>
-      <c r="E108" s="8"/>
-      <c r="F108" s="8"/>
-      <c r="G108" s="8"/>
-      <c r="H108" s="8"/>
-      <c r="I108" s="8"/>
-      <c r="J108" s="8"/>
-      <c r="K108" s="8"/>
-      <c r="L108" s="8"/>
-      <c r="M108" s="8"/>
-      <c r="N108" s="8"/>
+      <c r="A108" s="11"/>
+      <c r="B108" s="12"/>
+      <c r="C108" s="12"/>
+      <c r="D108" s="12"/>
+      <c r="E108" s="12"/>
+      <c r="F108" s="12"/>
+      <c r="G108" s="12"/>
+      <c r="H108" s="12"/>
+      <c r="I108" s="12"/>
+      <c r="J108" s="12"/>
+      <c r="K108" s="12"/>
+      <c r="L108" s="12"/>
+      <c r="M108" s="12"/>
+      <c r="N108" s="12"/>
     </row>
     <row r="109" spans="1:14">
-      <c r="A109" s="7"/>
-      <c r="B109" s="8"/>
-      <c r="C109" s="8"/>
-      <c r="D109" s="8"/>
-      <c r="E109" s="8"/>
-      <c r="F109" s="8"/>
-      <c r="G109" s="8"/>
-      <c r="H109" s="8"/>
-      <c r="I109" s="8"/>
-      <c r="J109" s="8"/>
-      <c r="K109" s="8"/>
-      <c r="L109" s="8"/>
-      <c r="M109" s="8"/>
-      <c r="N109" s="8"/>
+      <c r="A109" s="11"/>
+      <c r="B109" s="12"/>
+      <c r="C109" s="12"/>
+      <c r="D109" s="12"/>
+      <c r="E109" s="12"/>
+      <c r="F109" s="12"/>
+      <c r="G109" s="12"/>
+      <c r="H109" s="12"/>
+      <c r="I109" s="12"/>
+      <c r="J109" s="12"/>
+      <c r="K109" s="12"/>
+      <c r="L109" s="12"/>
+      <c r="M109" s="12"/>
+      <c r="N109" s="12"/>
     </row>
     <row r="110" spans="1:14">
-      <c r="A110" s="7"/>
-      <c r="B110" s="8"/>
-      <c r="C110" s="8"/>
-      <c r="D110" s="8"/>
-      <c r="E110" s="8"/>
-      <c r="F110" s="8"/>
-      <c r="G110" s="8"/>
-      <c r="H110" s="8"/>
-      <c r="I110" s="8"/>
-      <c r="J110" s="8"/>
-      <c r="K110" s="8"/>
-      <c r="L110" s="8"/>
-      <c r="M110" s="8"/>
-      <c r="N110" s="8"/>
+      <c r="A110" s="11"/>
+      <c r="B110" s="12"/>
+      <c r="C110" s="12"/>
+      <c r="D110" s="12"/>
+      <c r="E110" s="12"/>
+      <c r="F110" s="12"/>
+      <c r="G110" s="12"/>
+      <c r="H110" s="12"/>
+      <c r="I110" s="12"/>
+      <c r="J110" s="12"/>
+      <c r="K110" s="12"/>
+      <c r="L110" s="12"/>
+      <c r="M110" s="12"/>
+      <c r="N110" s="12"/>
     </row>
     <row r="111" spans="1:14">
-      <c r="A111" s="7"/>
-      <c r="B111" s="8"/>
-      <c r="C111" s="8"/>
-      <c r="D111" s="8"/>
-      <c r="E111" s="8"/>
-      <c r="F111" s="8"/>
-      <c r="G111" s="8"/>
-      <c r="H111" s="8"/>
-      <c r="I111" s="8"/>
-      <c r="J111" s="8"/>
-      <c r="K111" s="8"/>
-      <c r="L111" s="8"/>
-      <c r="M111" s="8"/>
-      <c r="N111" s="8"/>
+      <c r="A111" s="11"/>
+      <c r="B111" s="12"/>
+      <c r="C111" s="12"/>
+      <c r="D111" s="12"/>
+      <c r="E111" s="12"/>
+      <c r="F111" s="12"/>
+      <c r="G111" s="12"/>
+      <c r="H111" s="12"/>
+      <c r="I111" s="12"/>
+      <c r="J111" s="12"/>
+      <c r="K111" s="12"/>
+      <c r="L111" s="12"/>
+      <c r="M111" s="12"/>
+      <c r="N111" s="12"/>
     </row>
     <row r="112" spans="1:14">
-      <c r="A112" s="7"/>
-      <c r="B112" s="8"/>
-      <c r="C112" s="8"/>
-      <c r="D112" s="8"/>
-      <c r="E112" s="8"/>
-      <c r="F112" s="8"/>
-      <c r="G112" s="8"/>
-      <c r="H112" s="8"/>
-      <c r="I112" s="8"/>
-      <c r="J112" s="8"/>
-      <c r="K112" s="8"/>
-      <c r="L112" s="8"/>
-      <c r="M112" s="8"/>
-      <c r="N112" s="8"/>
+      <c r="A112" s="11"/>
+      <c r="B112" s="12"/>
+      <c r="C112" s="12"/>
+      <c r="D112" s="12"/>
+      <c r="E112" s="12"/>
+      <c r="F112" s="12"/>
+      <c r="G112" s="12"/>
+      <c r="H112" s="12"/>
+      <c r="I112" s="12"/>
+      <c r="J112" s="12"/>
+      <c r="K112" s="12"/>
+      <c r="L112" s="12"/>
+      <c r="M112" s="12"/>
+      <c r="N112" s="12"/>
+    </row>
+    <row r="113" spans="1:14">
+      <c r="A113" s="11"/>
+      <c r="B113" s="12"/>
+      <c r="C113" s="12"/>
+      <c r="D113" s="12"/>
+      <c r="E113" s="12"/>
+      <c r="F113" s="12"/>
+      <c r="G113" s="12"/>
+      <c r="H113" s="12"/>
+      <c r="I113" s="12"/>
+      <c r="J113" s="12"/>
+      <c r="K113" s="12"/>
+      <c r="L113" s="12"/>
+      <c r="M113" s="12"/>
+      <c r="N113" s="12"/>
+    </row>
+    <row r="114" spans="1:14">
+      <c r="A114" s="11"/>
+      <c r="B114" s="12"/>
+      <c r="C114" s="12"/>
+      <c r="D114" s="12"/>
+      <c r="E114" s="12"/>
+      <c r="F114" s="12"/>
+      <c r="G114" s="12"/>
+      <c r="H114" s="12"/>
+      <c r="I114" s="12"/>
+      <c r="J114" s="12"/>
+      <c r="K114" s="12"/>
+      <c r="L114" s="12"/>
+      <c r="M114" s="12"/>
+      <c r="N114" s="12"/>
+    </row>
+    <row r="115" spans="1:14">
+      <c r="A115" s="11"/>
+      <c r="B115" s="12"/>
+      <c r="C115" s="12"/>
+      <c r="D115" s="12"/>
+      <c r="E115" s="12"/>
+      <c r="F115" s="12"/>
+      <c r="G115" s="12"/>
+      <c r="H115" s="12"/>
+      <c r="I115" s="12"/>
+      <c r="J115" s="12"/>
+      <c r="K115" s="12"/>
+      <c r="L115" s="12"/>
+      <c r="M115" s="12"/>
+      <c r="N115" s="12"/>
+    </row>
+    <row r="116" spans="1:14">
+      <c r="A116" s="11"/>
+      <c r="B116" s="12"/>
+      <c r="C116" s="12"/>
+      <c r="D116" s="12"/>
+      <c r="E116" s="12"/>
+      <c r="F116" s="12"/>
+      <c r="G116" s="12"/>
+      <c r="H116" s="12"/>
+      <c r="I116" s="12"/>
+      <c r="J116" s="12"/>
+      <c r="K116" s="12"/>
+      <c r="L116" s="12"/>
+      <c r="M116" s="12"/>
+      <c r="N116" s="12"/>
+    </row>
+    <row r="117" spans="1:14">
+      <c r="A117" s="11"/>
+      <c r="B117" s="12"/>
+      <c r="C117" s="12"/>
+      <c r="D117" s="12"/>
+      <c r="E117" s="12"/>
+      <c r="F117" s="12"/>
+      <c r="G117" s="12"/>
+      <c r="H117" s="12"/>
+      <c r="I117" s="12"/>
+      <c r="J117" s="12"/>
+      <c r="K117" s="12"/>
+      <c r="L117" s="12"/>
+      <c r="M117" s="12"/>
+      <c r="N117" s="12"/>
+    </row>
+    <row r="118" spans="1:14">
+      <c r="A118" s="11"/>
+      <c r="B118" s="12"/>
+      <c r="C118" s="12"/>
+      <c r="D118" s="12"/>
+      <c r="E118" s="12"/>
+      <c r="F118" s="12"/>
+      <c r="G118" s="12"/>
+      <c r="H118" s="12"/>
+      <c r="I118" s="12"/>
+      <c r="J118" s="12"/>
+      <c r="K118" s="12"/>
+      <c r="L118" s="12"/>
+      <c r="M118" s="12"/>
+      <c r="N118" s="12"/>
+    </row>
+    <row r="119" spans="1:14">
+      <c r="A119" s="11"/>
+      <c r="B119" s="12"/>
+      <c r="C119" s="12"/>
+      <c r="D119" s="12"/>
+      <c r="E119" s="12"/>
+      <c r="F119" s="12"/>
+      <c r="G119" s="12"/>
+      <c r="H119" s="12"/>
+      <c r="I119" s="12"/>
+      <c r="J119" s="12"/>
+      <c r="K119" s="12"/>
+      <c r="L119" s="12"/>
+      <c r="M119" s="12"/>
+      <c r="N119" s="12"/>
+    </row>
+    <row r="120" spans="1:14">
+      <c r="A120" s="11"/>
+      <c r="B120" s="12"/>
+      <c r="C120" s="12"/>
+      <c r="D120" s="12"/>
+      <c r="E120" s="12"/>
+      <c r="F120" s="12"/>
+      <c r="G120" s="12"/>
+      <c r="H120" s="12"/>
+      <c r="I120" s="12"/>
+      <c r="J120" s="12"/>
+      <c r="K120" s="12"/>
+      <c r="L120" s="12"/>
+      <c r="M120" s="12"/>
+      <c r="N120" s="12"/>
+    </row>
+    <row r="121" spans="1:14">
+      <c r="A121" s="11"/>
+      <c r="B121" s="12"/>
+      <c r="C121" s="12"/>
+      <c r="D121" s="12"/>
+      <c r="E121" s="12"/>
+      <c r="F121" s="12"/>
+      <c r="G121" s="12"/>
+      <c r="H121" s="12"/>
+      <c r="I121" s="12"/>
+      <c r="J121" s="12"/>
+      <c r="K121" s="12"/>
+      <c r="L121" s="12"/>
+      <c r="M121" s="12"/>
+      <c r="N121" s="12"/>
+    </row>
+    <row r="122" spans="1:14">
+      <c r="A122" s="11"/>
+      <c r="B122" s="12"/>
+      <c r="C122" s="12"/>
+      <c r="D122" s="12"/>
+      <c r="E122" s="12"/>
+      <c r="F122" s="12"/>
+      <c r="G122" s="12"/>
+      <c r="H122" s="12"/>
+      <c r="I122" s="12"/>
+      <c r="J122" s="12"/>
+      <c r="K122" s="12"/>
+      <c r="L122" s="12"/>
+      <c r="M122" s="12"/>
+      <c r="N122" s="12"/>
+    </row>
+    <row r="123" spans="1:14">
+      <c r="A123" s="11"/>
+      <c r="B123" s="12"/>
+      <c r="C123" s="12"/>
+      <c r="D123" s="12"/>
+      <c r="E123" s="12"/>
+      <c r="F123" s="12"/>
+      <c r="G123" s="12"/>
+      <c r="H123" s="12"/>
+      <c r="I123" s="12"/>
+      <c r="J123" s="12"/>
+      <c r="K123" s="12"/>
+      <c r="L123" s="12"/>
+      <c r="M123" s="12"/>
+      <c r="N123" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
